--- a/scenic/summary/outputs/三景区景区指南数据集.xlsx
+++ b/scenic/summary/outputs/三景区景区指南数据集.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28 20:26:48</t>
+          <t>2026-10-28 20:34:25</t>
         </is>
       </c>
     </row>

--- a/scenic/summary/outputs/三景区景区指南数据集.xlsx
+++ b/scenic/summary/outputs/三景区景区指南数据集.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28 20:34:25</t>
+          <t>2026-10-28 20:49:31</t>
         </is>
       </c>
     </row>
@@ -823,202 +823,103 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;嗨！各位快乐玩家，欢迎来到广州长隆度假区，快收下这份吃住玩一站式度假攻略，一键开启快乐假日吧！&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:center;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;b&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;第一站：长隆欢乐世界&lt;/span&gt;&lt;/span&gt;&lt;/b&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:center;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;假期想狂欢？那就来广州长隆欢乐世界！忘掉工作的繁忙和生活的琐碎，来一场全身心的狂欢刺激之旅吧。这里有全球领先的70+游乐设施，有趣，好看又刺激，让你心跳加速尽情释放！ &lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;坐上“全球过山车之王“的垂直过山车。三分钟之内让你完成上天入地冲浪的刺激体验&lt;/span&gt;&lt;/span&gt; &lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;div class="list-img-wrap"&gt;
-&lt;ul class="row list-img"&gt;&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/czgsc1.393645f.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/czgsc2.1062028.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;/ul&gt;&lt;/div&gt;
-&lt;p style="text-align:center;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;坐上游乐园最大的秋千，挑战地心引力 在超级大摆锤的极致摇摆中，感受无尽的刺激和乐趣 &lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt; &lt;/div&gt;
-&lt;div class="list-img-wrap"&gt;
-&lt;ul class="row list-img"&gt;&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/cjdbc1.99578e7.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/cjdbc2.65d4f90.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;/ul&gt;&lt;/div&gt;
-&lt;div class="text-wrap"&gt; &lt;/div&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;谁说欢乐世界只适合大朋友，这里有小朋友也能玩的飞马家庭过山车，刺激又奇幻，家庭出游千万不要错过。最浪漫的打卡点还是梦幻转马，无论是小朋友还是拥有少女心的你，都可以进入梦幻童话世界， 打卡到人生照片&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt; &lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/mhzm1.23a35f5.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt; &lt;/div&gt;
-&lt;p style="text-align:center;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;b&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;第二站：长隆野生动物世界&lt;/span&gt;&lt;/span&gt;&lt;/b&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:center;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;来都来了，怎么能错过长隆野生动物世界~珍稀的动物大家族，独特的观赏方式和精彩的科普课堂，各种超好玩的项目等你来打卡 &lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:center;"&gt; &lt;/p&gt;
-&lt;p style="text-align:center;"&gt; &lt;/p&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/kzlc1.40f8bcf.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt; &lt;/div&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;搭乘缆车飞跃东非大草原，俯瞰壮观的动物大迁徙。在长颈鹿广场，可以给长颈鹿投喂树叶，与它互动拍照打卡&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/cjlgc1.27fdc07.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt; &lt;/div&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;乘坐森林小火车，穿越五大洲的珍稀动物世界，近距离接触可爱的动物朋友&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:center;"&gt; &lt;/p&gt;
-&lt;div class="list-img-wrap"&gt;
-&lt;ul class="row list-img"&gt;&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="266e8bad2e088404.jpg" src="https://cdn.chimelong.com/upload/eaa5ec555452a0a4/266e8bad2e088404.jpg" title="image"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/xhcyl2.43f032c.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;/ul&gt;&lt;/div&gt;
-&lt;div class="text-wrap"&gt; &lt;/div&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;喜欢大熊猫的小朋友千万别错过，拥有全球唯一大熊猫三胞胎的熊猫村。熊猫三宝今年就10周岁啦，小朋友们记得来参加萌帅酷的十周岁生日呀！&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/xmly1.a586251.jpg"/&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;考拉园也同样值得游玩，考拉大家族八代同堂，同时还是北半球至大的考拉大种群&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/kly1.baf2827.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt; &lt;/div&gt;
-&lt;p style="text-align:center;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;b&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;第三站：长隆水上乐园&lt;/span&gt;&lt;/span&gt;&lt;/b&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:center;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;夏天的正确打开方式，当然是来广州长隆水上乐园玩水啦！超过70套顶级设备为玩水家们带来无尽的欢乐与惊喜 &lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:center;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;摇滚巨轮是长隆水上乐园跨时代的玩水设施，一出道就迅速爆红，获得多个国际行业大奖。在这里你可以体验到360°漂移，俯冲快感，收获前所未有的玩水体验&lt;/span&gt;&lt;/span&gt; &lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:center;"&gt;&lt;img alt="fc3a5c84b5cddfbc.gif" class="img-responsive" src="https://cdn.chimelong.com/upload/6c73256b6a59a2bd/fc3a5c84b5cddfbc.gif" title="image"/&gt;&lt;/p&gt;
-&lt;p&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;白天没玩够？来超级造浪池，九种海浪模式为玩水家带来全海域体验，晚上还有水上电音节，绚丽的烟花，酷炫的灯光和炸裂的音效，配合行业顶尖DJ/MC驻场，点燃每一晚的电音狂潮，跟着节奏不断摇摆，来一场独一无二的水上蹦迪 &lt;/span&gt;&lt;/span&gt; &lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:center;"&gt;&lt;img alt="78cef3af6a1828cd.gif" class="img-responsive" src="https://cdn.chimelong.com/upload/362f338ee933c99f/78cef3af6a1828cd.gif" title="image"/&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;关于饮食&lt;/strong&gt;&lt;/div&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;野生动物世界推荐：熊猫餐厅&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;熊猫乐园旁边的熊猫餐厅就是一个解决午餐的好地方，可以和可爱的熊猫宝宝一起吃午饭。&lt;/div&gt;
-&lt;/div&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/xmct1.0194a95.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt; &lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;欢乐世界：椰林餐厅&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;椰林餐厅，有地道的粤式美食滋味咸香鸡和东南亚风味的泰式风情沙拉菜式，让您吃的生态，品的自然。还有现烤的正宗德克萨斯牛柳焦香味浓，肉质鲜嫩，一定会让您垂涎欲滴！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/upload/17189bc3c67f1bb8/3930f1515ca1919d.jpg"/&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;关于住宿&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;广州长隆熊猫酒店&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;【入住温馨提示】&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;1.记得提前准备好所有入住人的有效证件哦~&lt;/div&gt;
-&lt;div class="text p"&gt;2.第二个重要的事情就是去拿行李啦！请凭房号前往礼宾部~&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;四大主题房：&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;卡哇伊的粉红“萌萌房”，最适合甜美范儿的小可爱~&lt;/div&gt;
-&lt;div class="text p"&gt;奔放热烈的红色“帅帅房”，瞬间穿越童话二次元！&lt;/div&gt;
-&lt;div class="text p"&gt;充满朝气的橙色“酷酷房”，让人感觉活力满满！&lt;/div&gt;
-&lt;div class="text p"&gt;还有童心爆棚的王子家庭房，这个就特别适合家庭居住啦！&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="list-img-wrap"&gt;
-&lt;ul class="row list-img"&gt;&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/xmjdztf1.65b0a82.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/xmjdztf2.8028a2e.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/xmjdztf3.ba8200b.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/xmjdztf4.6dae13a.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;/ul&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;广州长隆酒店&lt;/strong&gt;&lt;/div&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;div class="text p"&gt;探趣亲子房&lt;/div&gt;
-&lt;div class="text p"&gt;为多胎家庭贴心设计的亲子房，大胆融入各种动物主题，仿佛身临其境置身动物家园之余，大人小朋友都还可以拥有自己的专属小空间。房间更多隐藏细节彩蛋带您发现，更贴心准备小童专属用品，快来这里度过美好的亲子时光吧！&lt;/div&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/upload/9d76f17abc5fdee8/88d7b99adfc31bfe.jpg"/&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;关于交通&lt;/strong&gt;&lt;/div&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;速速收下这份交通指南，让你轻轻松松来广州长隆！&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;&lt;strong&gt;机场接驳：&lt;/strong&gt;从广州白云机场出发搭乘机场快线约1小时15分钟直达广州长隆度假旅游区。&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;&lt;strong&gt;高铁轻轨：&lt;/strong&gt;从广州南高铁站出发搭乘地铁7号线到达汉溪长隆地铁站（E出口）；从广州东高铁站出发搭乘地铁3号线北延段到达体育西地铁站转3号线到达汉溪长隆地铁站（E出口）；从广州火车站地铁站出发搭乘地铁5号线到达珠江新城站转3号线到达汉溪长隆地铁站（E出口）。&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;&lt;strong&gt;地铁：&lt;/strong&gt;从广州各地铁站点搭乘至3号线或7号线（E出口）。&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;&lt;strong&gt;公交巴士：&lt;/strong&gt;129路，番163路，番109路，304路。&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p&gt; &lt;/p&gt;
-&lt;/div&gt; </t>
+          <t>嗨！各位快乐玩家，欢迎来到广州长隆度假区，快收下这份吃住玩一站式度假攻略，一键开启快乐假日吧！
+第一站：长隆欢乐世界
+假期想狂欢？那就来广州长隆欢乐世界！忘掉工作的繁忙和生活的琐碎，来一场全身心的狂欢刺激之旅吧。这里有全球领先的70+游乐设施，有趣，好看又刺激，让你心跳加速尽情释放！
+坐上“全球过山车之王“的垂直过山车。三分钟之内让你完成上天入地冲浪的刺激体验
+坐上游乐园最大的秋千，挑战地心引力 在超级大摆锤的极致摇摆中，感受无尽的刺激和乐趣
+谁说欢乐世界只适合大朋友，这里有小朋友也能玩的飞马家庭过山车，刺激又奇幻，家庭出游千万不要错过。最浪漫的打卡点还是梦幻转马，无论是小朋友还是拥有少女心的你，都可以进入梦幻童话世界， 打卡到人生照片
+第二站：长隆野生动物世界
+来都来了，怎么能错过长隆野生动物世界~珍稀的动物大家族，独特的观赏方式和精彩的科普课堂，各种超好玩的项目等你来打卡
+搭乘缆车飞跃东非大草原，俯瞰壮观的动物大迁徙。在长颈鹿广场，可以给长颈鹿投喂树叶，与它互动拍照打卡
+乘坐森林小火车，穿越五大洲的珍稀动物世界，近距离接触可爱的动物朋友
+喜欢大熊猫的小朋友千万别错过，拥有全球唯一大熊猫三胞胎的熊猫村。熊猫三宝今年就10周岁啦，小朋友们记得来参加萌帅酷的十周岁生日呀！
+考拉园也同样值得游玩，考拉大家族八代同堂，同时还是北半球至大的考拉大种群
+第三站：长隆水上乐园
+夏天的正确打开方式，当然是来广州长隆水上乐园玩水啦！超过70套顶级设备为玩水家们带来无尽的欢乐与惊喜
+摇滚巨轮是长隆水上乐园跨时代的玩水设施，一出道就迅速爆红，获得多个国际行业大奖。在这里你可以体验到360°漂移，俯冲快感，收获前所未有的玩水体验
+白天没玩够？来超级造浪池，九种海浪模式为玩水家带来全海域体验，晚上还有水上电音节，绚丽的烟花，酷炫的灯光和炸裂的音效，配合行业顶尖DJ/MC驻场，点燃每一晚的电音狂潮，跟着节奏不断摇摆，来一场独一无二的水上蹦迪
+关于饮食
+野生动物世界推荐：熊猫餐厅
+熊猫乐园旁边的熊猫餐厅就是一个解决午餐的好地方，可以和可爱的熊猫宝宝一起吃午饭。
+欢乐世界：椰林餐厅
+椰林餐厅，有地道的粤式美食滋味咸香鸡和东南亚风味的泰式风情沙拉菜式，让您吃的生态，品的自然。还有现烤的正宗德克萨斯牛柳焦香味浓，肉质鲜嫩，一定会让您垂涎欲滴！
+关于住宿
+广州长隆熊猫酒店
+【入住温馨提示】
+1.记得提前准备好所有入住人的有效证件哦~
+2.第二个重要的事情就是去拿行李啦！请凭房号前往礼宾部~
+四大主题房：
+卡哇伊的粉红“萌萌房”，最适合甜美范儿的小可爱~
+奔放热烈的红色“帅帅房”，瞬间穿越童话二次元！
+充满朝气的橙色“酷酷房”，让人感觉活力满满！
+还有童心爆棚的王子家庭房，这个就特别适合家庭居住啦！
+广州长隆酒店
+探趣亲子房
+为多胎家庭贴心设计的亲子房，大胆融入各种动物主题，仿佛身临其境置身动物家园之余，大人小朋友都还可以拥有自己的专属小空间。房间更多隐藏细节彩蛋带您发现，更贴心准备小童专属用品，快来这里度过美好的亲子时光吧！
+关于交通
+速速收下这份交通指南，让你轻轻松松来广州长隆！
+机场接驳：从广州白云机场出发搭乘机场快线约1小时15分钟直达广州长隆度假旅游区。
+高铁轻轨：从广州南高铁站出发搭乘地铁7号线到达汉溪长隆地铁站（E出口）；从广州东高铁站出发搭乘地铁3号线北延段到达体育西地铁站转3号线到达汉溪长隆地铁站（E出口）；从广州火车站地铁站出发搭乘地铁5号线到达珠江新城站转3号线到达汉溪长隆地铁站（E出口）。
+地铁：从广州各地铁站点搭乘至3号线或7号线（E出口）。
+公交巴士：129路，番163路，番109路，304路。</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>嗨！各位快乐玩家，欢迎来到广州长隆度假区，快收下这份吃住玩一站式度假攻略，一键开启快乐假日吧！
-第一站：长隆欢乐世界
-假期想狂欢？那就来广州长隆欢乐世界！忘掉工作的繁忙和生活的琐碎，来一场全身心的狂欢刺激之旅吧。这里有全球领先的70+游乐设施，有趣，好看又刺激，让你心跳加速尽情释放！
-坐上“全球过山车之王“的垂直过山车。三分钟之内让你完成上天入地冲浪的刺激体验
-坐上游乐园最大的秋千，挑战地心引力 在超级大摆锤的极致摇摆中，感受无尽的刺激和乐趣
-谁说欢乐世界只适合大朋友，这里有小朋友也能玩的飞马家庭过山车，刺激又奇幻，家庭出游千万不要错过。最浪漫的打卡点还是梦幻转马，无论是小朋友还是拥有少女心的你，都可以进入梦幻童话世界，打卡到人生照片
-第二站：长隆野生动物世界
-来都来了，怎么能错过长隆野生动物世界~珍稀的动物大家族，独特的观赏方式和精彩的科普课堂，各种超好玩的项目等你来打卡
-搭乘缆车飞跃东非大草原，俯瞰壮观的动物大迁徙。在长颈鹿广场，可以给长颈鹿投喂树叶，与它互动拍照打卡
-乘坐森林小火车，穿越五大洲的珍稀动物世界，近距离接触可爱的动物朋友
-喜欢大熊猫的小朋友千万别错过，拥有全球唯一大熊猫三胞胎的熊猫村。熊猫三宝今年就10周岁啦，小朋友们记得来参加萌帅酷的十周岁生日呀！
-考拉园也同样值得游玩，考拉大家族八代同堂，同时还是北半球至大的考拉大种群
-第三站：长隆水上乐园
-夏天的正确打开方式，当然是来广州长隆水上乐园玩水啦！超过70套顶级设备为玩水家们带来无尽的欢乐与惊喜
-摇滚巨轮是长隆水上乐园跨时代的玩水设施，一出道就迅速爆红，获得多个国际行业大奖。在这里你可以体验到360°漂移，俯冲快感，收获前所未有的玩水体验
-白天没玩够？来超级造浪池，九种海浪模式为玩水家带来全海域体验，晚上还有水上电音节，绚丽的烟花，酷炫的灯光和炸裂的音效，配合行业顶尖DJ/MC驻场，点燃每一晚的电音狂潮，跟着节奏不断摇摆，来一场独一无二的水上蹦迪
-关于饮食
-野生动物世界推荐：熊猫餐厅
-熊猫乐园旁边的熊猫餐厅就是一个解决午餐的好地方，可以和可爱的熊猫宝宝一起吃午饭。
-欢乐世界：椰林餐厅
-椰林餐厅，有地道的粤式美食滋味咸香鸡和东南亚风味的泰式风情沙拉菜式，让您吃的生态，品的自然。还有现烤的正宗德克萨斯牛柳焦香味浓，肉质鲜嫩，一定会让您垂涎欲滴！
-关于住宿
-广州长隆熊猫酒店
-【入住温馨提示】
-1.记得提前准备好所有入住人的有效证件哦~
-2.第二个重要的事情就是去拿行李啦！请凭房号前往礼宾部~
-四大主题房
-卡哇伊的粉红“萌萌房”，最适合甜美范儿的小可爱~
-奔放热烈的红色“帅帅房”，瞬间穿越童话二次元！
-充满朝气的橙色“酷酷房”，让人感觉活力满满！
-还有童心爆棚的王子家庭房，这个就特别适合家庭居住啦！
-广州长隆酒店
-探趣亲子房
-为多胎家庭贴心设计的亲子房，大胆融入各种动物主题，仿佛身临其境置身动物家园之余，大人小朋友都还可以拥有自己的专属小空间。房间更多隐藏细节彩蛋带您发现，更贴心准备小童专属用品，快来这里度过美好的亲子时光吧！
-关于交通
-速速收下这份交通指南，让你轻轻松松来广州长隆！
-机场接驳：从广州白云机场出发搭乘机场快线约1小时15分钟直达广州长隆度假旅游区。
-高铁轻轨：从广州南高铁站出发搭乘地铁7号线到达汉溪长隆地铁站（E出口）；从广州东高铁站出发搭乘地铁3号线北延段到达体育西地铁站转3号线到达汉溪长隆地铁站（E出口）；从广州火车站地铁站出发搭乘地铁5号线到达珠江新城站转3号线到达汉溪长隆地铁站（E出口）。
-地铁：从广州各地铁站点搭乘至3号线或7号线（E出口）。
+          <t>嗨！各位快乐玩家，欢迎来到广州长隆度假区，快收下这份吃住玩一站式度假攻略，一键开启快乐假日吧！
+第一站：长隆欢乐世界
+假期想狂欢？那就来广州长隆欢乐世界！忘掉工作的繁忙和生活的琐碎，来一场全身心的狂欢刺激之旅吧。这里有全球领先的70+游乐设施，有趣，好看又刺激，让你心跳加速尽情释放！
+坐上“全球过山车之王“的垂直过山车。三分钟之内让你完成上天入地冲浪的刺激体验
+坐上游乐园最大的秋千，挑战地心引力 在超级大摆锤的极致摇摆中，感受无尽的刺激和乐趣
+谁说欢乐世界只适合大朋友，这里有小朋友也能玩的飞马家庭过山车，刺激又奇幻，家庭出游千万不要错过。最浪漫的打卡点还是梦幻转马，无论是小朋友还是拥有少女心的你，都可以进入梦幻童话世界，打卡到人生照片
+第二站：长隆野生动物世界
+来都来了，怎么能错过长隆野生动物世界~珍稀的动物大家族，独特的观赏方式和精彩的科普课堂，各种超好玩的项目等你来打卡
+搭乘缆车飞跃东非大草原，俯瞰壮观的动物大迁徙。在长颈鹿广场，可以给长颈鹿投喂树叶，与它互动拍照打卡
+乘坐森林小火车，穿越五大洲的珍稀动物世界，近距离接触可爱的动物朋友
+喜欢大熊猫的小朋友千万别错过，拥有全球唯一大熊猫三胞胎的熊猫村。熊猫三宝今年就10周岁啦，小朋友们记得来参加萌帅酷的十周岁生日呀！
+考拉园也同样值得游玩，考拉大家族八代同堂，同时还是北半球至大的考拉大种群
+第三站：长隆水上乐园
+夏天的正确打开方式，当然是来广州长隆水上乐园玩水啦！超过70套顶级设备为玩水家们带来无尽的欢乐与惊喜
+摇滚巨轮是长隆水上乐园跨时代的玩水设施，一出道就迅速爆红，获得多个国际行业大奖。在这里你可以体验到360°漂移，俯冲快感，收获前所未有的玩水体验
+白天没玩够？来超级造浪池，九种海浪模式为玩水家带来全海域体验，晚上还有水上电音节，绚丽的烟花，酷炫的灯光和炸裂的音效，配合行业顶尖DJ/MC驻场，点燃每一晚的电音狂潮，跟着节奏不断摇摆，来一场独一无二的水上蹦迪
+关于饮食
+野生动物世界推荐：熊猫餐厅
+熊猫乐园旁边的熊猫餐厅就是一个解决午餐的好地方，可以和可爱的熊猫宝宝一起吃午饭。
+欢乐世界：椰林餐厅
+椰林餐厅，有地道的粤式美食滋味咸香鸡和东南亚风味的泰式风情沙拉菜式，让您吃的生态，品的自然。还有现烤的正宗德克萨斯牛柳焦香味浓，肉质鲜嫩，一定会让您垂涎欲滴！
+关于住宿
+广州长隆熊猫酒店
+【入住温馨提示】
+1.记得提前准备好所有入住人的有效证件哦~
+2.第二个重要的事情就是去拿行李啦！请凭房号前往礼宾部~
+四大主题房
+卡哇伊的粉红“萌萌房”，最适合甜美范儿的小可爱~
+奔放热烈的红色“帅帅房”，瞬间穿越童话二次元！
+充满朝气的橙色“酷酷房”，让人感觉活力满满！
+还有童心爆棚的王子家庭房，这个就特别适合家庭居住啦！
+广州长隆酒店
+探趣亲子房
+为多胎家庭贴心设计的亲子房，大胆融入各种动物主题，仿佛身临其境置身动物家园之余，大人小朋友都还可以拥有自己的专属小空间。房间更多隐藏细节彩蛋带您发现，更贴心准备小童专属用品，快来这里度过美好的亲子时光吧！
+关于交通
+速速收下这份交通指南，让你轻轻松松来广州长隆！
+机场接驳：从广州白云机场出发搭乘机场快线约1小时15分钟直达广州长隆度假旅游区。
+高铁轻轨：从广州南高铁站出发搭乘地铁7号线到达汉溪长隆地铁站（E出口）；从广州东高铁站出发搭乘地铁3号线北延段到达体育西地铁站转3号线到达汉溪长隆地铁站（E出口）；从广州火车站地铁站出发搭乘地铁5号线到达珠江新城站转3号线到达汉溪长隆地铁站（E出口）。
+地铁：从广州各地铁站点搭乘至3号线或7号线（E出口）。
 公交巴士：129路，番163路，番109路，304路。</t>
         </is>
       </c>
       <c r="M2" s="5" t="n">
-        <v>10542</v>
+        <v>1479</v>
       </c>
       <c r="N2" s="5" t="n">
         <v>1478</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0.862</v>
+        <v>0.001</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="5" t="n">
         <v>0</v>
@@ -1093,145 +994,97 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;带上你爱的人，来长隆野生动物世界数动物，顺便来一场浪漫的空中告白&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;——长隆野生动物世界情侣游攻略&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;享用完早餐，可以凭房号前往礼宾部寄存行李，然后出门乘坐免费巴士到达长隆野生动物世界北门，我们打算从北门入园，先乘坐小火车游览一遍，然后一路向南，完美！&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;提前准备：&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;√现金（喂食的项目需要现金）&lt;/div&gt;
-&lt;div class="text p"&gt;√手机、相机、充电宝&lt;/div&gt;
-&lt;div class="text p"&gt;√太阳伞、防晒、防蚊喷雾（夏天）&lt;/div&gt;
-&lt;div class="text p"&gt;√饮用水（怕游客乱投食，除婴儿食品和每人限带一支（瓶）饮用水外，长隆各主题公园和马戏场馆谢绝游客（观众）带入其它食品和饮品）&lt;/div&gt;
-&lt;div class="text p"&gt;√另一半&lt;/div&gt;
-&lt;div class="text p"&gt; &lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;【游玩路线】&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;北门——小火车游览区——青龙山——考拉园——熊猫乐园——熊猫餐厅——4D影院——亚洲象园——长颈鹿广场——空中缆车——火烈鸟——南门纪念品商店——出园&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第一站（10:00）：小火车游览&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;从北门入园，在天鹅美食对面可以先乘坐小火车游玩乘车游览部分，游览时间大概30分钟，期间可以看到斑马、大象、长颈鹿、羊驼、狮子、狼、秃鹫、黑熊、羚羊等等，很多女孩子都对动物没有抵抗之力，在这里能一次性满足你对动物的喜爱哦！小火车中途不停车，是免费乘坐的哦，这么近距离地看这么多动物，很有声临其境的感觉，有点大胆的动物还会跟着车跑，感觉真的是超棒的！&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="list-img-wrap"&gt;
-&lt;ul class="row list-img"&gt;&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="266e8bad2e088404.jpg" src="https://cdn.chimelong.com/upload/eaa5ec555452a0a4/266e8bad2e088404.jpg" title="image"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/xhcyl2.43f032c.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;/ul&gt;&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第二站（11:00）：青龙山&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;小火车下来就是青龙山，按照路标我们来到了一直心心念念的侏罗纪森林，这个时候就是男朋友展示男友力的时候啦，逼真的特效还是让女孩子有点点小怕小怕的！森林里到处藏着恐龙，有的恐龙还会喷水，遇到喷水恐龙记得要躲开哦~期间还会穿过一个时空隧道，里面有两个超大的恐龙！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/qls1.3209fa4.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第三站（11:50）：考拉园&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;女孩子大部分都喜欢萌萌的动物，来到考拉园一定会敲开心！这是我们第一次看到这么萌的圆滚滚，光是盯着它们睡觉就能笑很久，还有一个看点就是看考拉吃树叶，吧唧吧唧吧唧的样子真香~连我都不由吞了下口水，额额，有点饿了！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/kly1.baf2827.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第四站（12:10）：熊猫乐园&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;除了可耐的考拉，还有男女通杀的大熊猫！简直迈不开脚步舍不得离开！天哪这个世界上怎么会有滚滚这么可爱的生物呢？看我迷离的眼神，身旁的TA说没见过你这么宠溺地看过我呢~除了三胞胎，还有其他团子，都是一副懒洋洋的样子，超级萌！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/xmly1.a586251.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第五站（12:30）：熊猫餐厅&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;刚好到了午饭时间，熊猫乐园旁边的熊猫餐厅就是一个解决午餐的好地方，因为可以和熊猫双胞胎亲亲爱爱一起吃午饭，而且套餐价格也还可以接受，七八十元起。吃完午餐可以看一看亲亲爱爱，这两只小家伙一直在打架，从树上打到树下，打的不亦乐乎，看的人也不亦乐乎！像极了平时一起打打闹闹的我们哈哈哈哈！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/xmct1.0194a95.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第六站（14:00）：4D影院&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;熊猫餐厅周边还有4D影院，刚好可以看看4D电影午休一下，顺便来一场跟平时不一样的电影约会哦~我们两个大孩子看得津津有味，4D的体验还是很神奇的，天上会飘下泡泡，打斗的剧情椅子还会跟着摇摆，有点刺激！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/4dyy1.3c32cca.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第七站（15:00）：亚洲象园&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;休息了一下，我们就要去喂大象啦！大象的口粮是香蕉，30元/五根！不知道是不是我的错觉，我感觉吃了香蕉的大象咧开嘴在微笑嘻嘻~在这里教大家一个大招，五根香蕉可以掰成十段，就可以喂十次啦！投食当然也是为了跟大象来个近距离合照，来一个不一样的秀恩爱方式~咔嚓！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/yzxy1.308db16.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第八站（15:30）：长颈鹿广场&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;大象旁边就是长颈鹿广场，也是可以投喂的！如果你实在不想花钱，我这里又有一招，那就是等别人在投喂的时候，立马咔嚓拍下长颈鹿跟你们的合照，是不是超级聪明哒！不过看长颈鹿的时候可要注意不要太近哦，不然可能会被长颈鹿的口水滴到哦~&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/cjlgc1.27fdc07.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第九站（16:00）：空中缆车&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;这个时候感觉已经走了好久好久，是时候休息一下了，于是空中缆车走起！空中缆车有两条路线：环园线和天鹅湖线！重点还是免费哦！这票价真的值了！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/kzlc1.40f8bcf.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;天鹅湖线&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;天鹅湖线是从熊猫乐园站——天鹅湖站的路线，缆车将低空横跨天鹅湖和鸳鸯湖，在缆车上俯瞰整个天鹅湖！听说天鹅一生严守一夫一妻制，若一方死亡，另一方则不食不眠，一意殉情！所以天鹅被视为忠诚和永恒爱情的象征。所以情侣们当然要来沾沾天鹅的美好祝愿~成双成对的天鹅，还有白鹭、海鸥等湖居动物朋友扑腾翅膀溅起水花，伴随湖风习习，真的是很舒服。&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/tehx1.a6eb1c1.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;环园线&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;建议大家坐环园线，也就是从熊猫乐园站——东非草原站——天鹅湖站——熊猫乐园站！整个路程大概30分钟，低空掠过整个园区时可以再看一遍动物，可以看到在奔腾的长颈鹿、跳羚、斑马等，还可以从空中看到考拉馆和熊猫乐园，记得跟住在半空中的团子们say hi哦！刚好是傍晚时分，可以跟最爱的人一起在夕阳下来张合照，简直不要太浪漫~&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="af56df792008e445.jpg" src="https://cdn.chimelong.com/upload/4b26f3741ce67587/af56df792008e445.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第十站（17:00）：看火烈鸟&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;坐完空中缆车，已经快到闭园时间啦！沿着路标往南门走，路上还能相遇很多小动物，其中就有风靡时尚圈的火烈鸟！红红火火真的是太耀眼了，有红的白的，太美了！看着看着旁边的傻货突然神秘兮兮地问我你知道为什么火烈鸟有的是白色有的是红色吗？“不知道哇”“那我就勉为其难地跟你科普一下”然后巴拉巴拉讲了一通之后：怎么样，现在是不是觉得本公子特别博学~看来是做足了功课额！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/khln1.a9f571a.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;第十一站（17:30）：南门纪念品商场&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;看了这么多萌萌的动物，肯定想把可爱的动物带回家！最后可以到南门的纪念品商场逛一逛，各自为对方选购精美可爱的动物玩具和礼品，在带走和动物们的美丽回忆的同时，把动物玩具带回家，以后看到这些可爱的小玩意就会想起这段美好记忆呢！&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/nmjnpsc1.7f03b00.jpg"/&gt;&lt;/p&gt; </t>
+          <t>带上你爱的人，来长隆野生动物世界数动物，顺便来一场浪漫的空中告白
+——长隆野生动物世界情侣游攻略
+享用完早餐，可以凭房号前往礼宾部寄存行李，然后出门乘坐免费巴士到达长隆野生动物世界北门，我们打算从北门入园，先乘坐小火车游览一遍，然后一路向南，完美！
+提前准备：
+√现金（喂食的项目需要现金）
+√手机、相机、充电宝
+√太阳伞、防晒、防蚊喷雾（夏天）
+√饮用水（怕游客乱投食，除婴儿食品和每人限带一支（瓶）饮用水外，长隆各主题公园和马戏场馆谢绝游客（观众）带入其它食品和饮品）
+√另一半
+【游玩路线】
+北门——小火车游览区——青龙山——考拉园——熊猫乐园——熊猫餐厅——4D影院——亚洲象园——长颈鹿广场——空中缆车——火烈鸟——南门纪念品商店——出园
+第一站（10:00）：小火车游览
+从北门入园，在天鹅美食对面可以先乘坐小火车游玩乘车游览部分，游览时间大概30分钟，期间可以看到斑马、大象、长颈鹿、羊驼、狮子、狼、秃鹫、黑熊、羚羊等等，很多女孩子都对动物没有抵抗之力，在这里能一次性满足你对动物的喜爱哦！小火车中途不停车，是免费乘坐的哦，这么近距离地看这么多动物，很有声临其境的感觉，有点大胆的动物还会跟着车跑，感觉真的是超棒的！
+第二站（11:00）：青龙山
+小火车下来就是青龙山，按照路标我们来到了一直心心念念的侏罗纪森林，这个时候就是男朋友展示男友力的时候啦，逼真的特效还是让女孩子有点点小怕小怕的！森林里到处藏着恐龙，有的恐龙还会喷水，遇到喷水恐龙记得要躲开哦~期间还会穿过一个时空隧道，里面有两个超大的恐龙！
+第三站（11:50）：考拉园
+女孩子大部分都喜欢萌萌的动物，来到考拉园一定会敲开心！这是我们第一次看到这么萌的圆滚滚，光是盯着它们睡觉就能笑很久，还有一个看点就是看考拉吃树叶，吧唧吧唧吧唧的样子真香~连我都不由吞了下口水，额额，有点饿了！
+第四站（12:10）：熊猫乐园
+除了可耐的考拉，还有男女通杀的大熊猫！简直迈不开脚步舍不得离开！天哪这个世界上怎么会有滚滚这么可爱的生物呢？看我迷离的眼神，身旁的TA说没见过你这么宠溺地看过我呢~除了三胞胎，还有其他团子，都是一副懒洋洋的样子，超级萌！
+第五站（12:30）：熊猫餐厅
+刚好到了午饭时间，熊猫乐园旁边的熊猫餐厅就是一个解决午餐的好地方，因为可以和熊猫双胞胎亲亲爱爱一起吃午饭，而且套餐价格也还可以接受，七八十元起。吃完午餐可以看一看亲亲爱爱，这两只小家伙一直在打架，从树上打到树下，打的不亦乐乎，看的人也不亦乐乎！像极了平时一起打打闹闹的我们哈哈哈哈！
+第六站（14:00）：4D影院
+熊猫餐厅周边还有4D影院，刚好可以看看4D电影午休一下，顺便来一场跟平时不一样的电影约会哦~我们两个大孩子看得津津有味，4D的体验还是很神奇的，天上会飘下泡泡，打斗的剧情椅子还会跟着摇摆，有点刺激！
+第七站（15:00）：亚洲象园
+休息了一下，我们就要去喂大象啦！大象的口粮是香蕉，30元/五根！不知道是不是我的错觉，我感觉吃了香蕉的大象咧开嘴在微笑嘻嘻~在这里教大家一个大招，五根香蕉可以掰成十段，就可以喂十次啦！投食当然也是为了跟大象来个近距离合照，来一个不一样的秀恩爱方式~咔嚓！
+第八站（15:30）：长颈鹿广场
+大象旁边就是长颈鹿广场，也是可以投喂的！如果你实在不想花钱，我这里又有一招，那就是等别人在投喂的时候，立马咔嚓拍下长颈鹿跟你们的合照，是不是超级聪明哒！不过看长颈鹿的时候可要注意不要太近哦，不然可能会被长颈鹿的口水滴到哦~
+第九站（16:00）：空中缆车
+这个时候感觉已经走了好久好久，是时候休息一下了，于是空中缆车走起！空中缆车有两条路线：环园线和天鹅湖线！重点还是免费哦！这票价真的值了！
+天鹅湖线
+天鹅湖线是从熊猫乐园站——天鹅湖站的路线，缆车将低空横跨天鹅湖和鸳鸯湖，在缆车上俯瞰整个天鹅湖！听说天鹅一生严守一夫一妻制，若一方死亡，另一方则不食不眠，一意殉情！所以天鹅被视为忠诚和永恒爱情的象征。所以情侣们当然要来沾沾天鹅的美好祝愿~成双成对的天鹅，还有白鹭、海鸥等湖居动物朋友扑腾翅膀溅起水花，伴随湖风习习，真的是很舒服。
+环园线
+建议大家坐环园线，也就是从熊猫乐园站——东非草原站——天鹅湖站——熊猫乐园站！整个路程大概30分钟，低空掠过整个园区时可以再看一遍动物，可以看到在奔腾的长颈鹿、跳羚、斑马等，还可以从空中看到考拉馆和熊猫乐园，记得跟住在半空中的团子们say hi哦！刚好是傍晚时分，可以跟最爱的人一起在夕阳下来张合照，简直不要太浪漫~
+第十站（17:00）：看火烈鸟
+坐完空中缆车，已经快到闭园时间啦！沿着路标往南门走，路上还能相遇很多小动物，其中就有风靡时尚圈的火烈鸟！红红火火真的是太耀眼了，有红的白的，太美了！看着看着旁边的傻货突然神秘兮兮地问我你知道为什么火烈鸟有的是白色有的是红色吗？“不知道哇”“那我就勉为其难地跟你科普一下”然后巴拉巴拉讲了一通之后：怎么样，现在是不是觉得本公子特别博学~看来是做足了功课额！
+第十一站（17:30）：南门纪念品商场
+看了这么多萌萌的动物，肯定想把可爱的动物带回家！最后可以到南门的纪念品商场逛一逛，各自为对方选购精美可爱的动物玩具和礼品，在带走和动物们的美丽回忆的同时，把动物玩具带回家，以后看到这些可爱的小玩意就会想起这段美好记忆呢！</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>带上你爱的人，来长隆野生动物世界数动物，顺便来一场浪漫的空中告白
-——长隆野生动物世界情侣游攻略
-享用完早餐，可以凭房号前往礼宾部寄存行李，然后出门乘坐免费巴士到达长隆野生动物世界北门，我们打算从北门入园，先乘坐小火车游览一遍，然后一路向南，完美！
-提前准备
-现金（喂食的项目需要现金）
-手机、相机、充电宝
-太阳伞、防晒、防蚊喷雾（夏天）
-饮用水（怕游客乱投食，除婴儿食品和每人限带一支（瓶）饮用水外，长隆各主题公园和马戏场馆谢绝游客（观众）带入其它食品和饮品）
-另一半
-【游玩路线】
-北门——小火车游览区——青龙山——考拉园——熊猫乐园——熊猫餐厅——4D影院——亚洲象园——长颈鹿广场——空中缆车——火烈鸟——南门纪念品商店——出园
-第一站（10:00）：小火车游览
-从北门入园，在天鹅美食对面可以先乘坐小火车游玩乘车游览部分，游览时间大概30分钟，期间可以看到斑马、大象、长颈鹿、羊驼、狮子、狼、秃鹫、黑熊、羚羊等等，很多女孩子都对动物没有抵抗之力，在这里能一次性满足你对动物的喜爱哦！小火车中途不停车，是免费乘坐的哦，这么近距离地看这么多动物，很有声临其境的感觉，有点大胆的动物还会跟着车跑，感觉真的是超棒的！
-第二站（11:00）：青龙山
-小火车下来就是青龙山，按照路标我们来到了一直心心念念的侏罗纪森林，这个时候就是男朋友展示男友力的时候啦，逼真的特效还是让女孩子有点点小怕小怕的！森林里到处藏着恐龙，有的恐龙还会喷水，遇到喷水恐龙记得要躲开哦~期间还会穿过一个时空隧道，里面有两个超大的恐龙！
-第三站（11:50）：考拉园
-女孩子大部分都喜欢萌萌的动物，来到考拉园一定会敲开心！这是我们第一次看到这么萌的圆滚滚，光是盯着它们睡觉就能笑很久，还有一个看点就是看考拉吃树叶，吧唧吧唧吧唧的样子真香~连我都不由吞了下口水，额额，有点饿了！
-第四站（12:10）：熊猫乐园
-除了可耐的考拉，还有男女通杀的大熊猫！简直迈不开脚步舍不得离开！天哪这个世界上怎么会有滚滚这么可爱的生物呢？看我迷离的眼神，身旁的TA说没见过你这么宠溺地看过我呢~除了三胞胎，还有其他团子，都是一副懒洋洋的样子，超级萌！
-第五站（12:30）：熊猫餐厅
-刚好到了午饭时间，熊猫乐园旁边的熊猫餐厅就是一个解决午餐的好地方，因为可以和熊猫双胞胎亲亲爱爱一起吃午饭，而且套餐价格也还可以接受，七八十元起。吃完午餐可以看一看亲亲爱爱，这两只小家伙一直在打架，从树上打到树下，打的不亦乐乎，看的人也不亦乐乎！像极了平时一起打打闹闹的我们哈哈哈哈！
-第六站（14:00）：4D影院
-熊猫餐厅周边还有4D影院，刚好可以看看4D电影午休一下，顺便来一场跟平时不一样的电影约会哦~我们两个大孩子看得津津有味，4D的体验还是很神奇的，天上会飘下泡泡，打斗的剧情椅子还会跟着摇摆，有点刺激！
-第七站（15:00）：亚洲象园
-休息了一下，我们就要去喂大象啦！大象的口粮是香蕉，30元/五根！不知道是不是我的错觉，我感觉吃了香蕉的大象咧开嘴在微笑嘻嘻~在这里教大家一个大招，五根香蕉可以掰成十段，就可以喂十次啦！投食当然也是为了跟大象来个近距离合照，来一个不一样的秀恩爱方式~咔嚓！
-第八站（15:30）：长颈鹿广场
-大象旁边就是长颈鹿广场，也是可以投喂的！如果你实在不想花钱，我这里又有一招，那就是等别人在投喂的时候，立马咔嚓拍下长颈鹿跟你们的合照，是不是超级聪明哒！不过看长颈鹿的时候可要注意不要太近哦，不然可能会被长颈鹿的口水滴到哦~
-第九站（16:00）：空中缆车
-这个时候感觉已经走了好久好久，是时候休息一下了，于是空中缆车走起！空中缆车有两条路线：环园线和天鹅湖线！重点还是免费哦！这票价真的值了！
-天鹅湖线
-天鹅湖线是从熊猫乐园站——天鹅湖站的路线，缆车将低空横跨天鹅湖和鸳鸯湖，在缆车上俯瞰整个天鹅湖！听说天鹅一生严守一夫一妻制，若一方死亡，另一方则不食不眠，一意殉情！所以天鹅被视为忠诚和永恒爱情的象征。所以情侣们当然要来沾沾天鹅的美好祝愿~成双成对的天鹅，还有白鹭、海鸥等湖居动物朋友扑腾翅膀溅起水花，伴随湖风习习，真的是很舒服。
-环园线
-建议大家坐环园线，也就是从熊猫乐园站——东非草原站——天鹅湖站——熊猫乐园站！整个路程大概30分钟，低空掠过整个园区时可以再看一遍动物，可以看到在奔腾的长颈鹿、跳羚、斑马等，还可以从空中看到考拉馆和熊猫乐园，记得跟住在半空中的团子们say hi哦！刚好是傍晚时分，可以跟最爱的人一起在夕阳下来张合照，简直不要太浪漫~
-第十站（17:00）：看火烈鸟
-坐完空中缆车，已经快到闭园时间啦！沿着路标往南门走，路上还能相遇很多小动物，其中就有风靡时尚圈的火烈鸟！红红火火真的是太耀眼了，有红的白的，太美了！看着看着旁边的傻货突然神秘兮兮地问我你知道为什么火烈鸟有的是白色有的是红色吗？“不知道哇”“那我就勉为其难地跟你科普一下”然后巴拉巴拉讲了一通之后：怎么样，现在是不是觉得本公子特别博学~看来是做足了功课额！
-第十一站（17:30）：南门纪念品商场
+          <t>带上你爱的人，来长隆野生动物世界数动物，顺便来一场浪漫的空中告白
+——长隆野生动物世界情侣游攻略
+享用完早餐，可以凭房号前往礼宾部寄存行李，然后出门乘坐免费巴士到达长隆野生动物世界北门，我们打算从北门入园，先乘坐小火车游览一遍，然后一路向南，完美！
+提前准备
+现金（喂食的项目需要现金）
+手机、相机、充电宝
+太阳伞、防晒、防蚊喷雾（夏天）
+饮用水（怕游客乱投食，除婴儿食品和每人限带一支（瓶）饮用水外，长隆各主题公园和马戏场馆谢绝游客（观众）带入其它食品和饮品）
+另一半
+【游玩路线】
+北门——小火车游览区——青龙山——考拉园——熊猫乐园——熊猫餐厅——4D影院——亚洲象园——长颈鹿广场——空中缆车——火烈鸟——南门纪念品商店——出园
+第一站（10:00）：小火车游览
+从北门入园，在天鹅美食对面可以先乘坐小火车游玩乘车游览部分，游览时间大概30分钟，期间可以看到斑马、大象、长颈鹿、羊驼、狮子、狼、秃鹫、黑熊、羚羊等等，很多女孩子都对动物没有抵抗之力，在这里能一次性满足你对动物的喜爱哦！小火车中途不停车，是免费乘坐的哦，这么近距离地看这么多动物，很有声临其境的感觉，有点大胆的动物还会跟着车跑，感觉真的是超棒的！
+第二站（11:00）：青龙山
+小火车下来就是青龙山，按照路标我们来到了一直心心念念的侏罗纪森林，这个时候就是男朋友展示男友力的时候啦，逼真的特效还是让女孩子有点点小怕小怕的！森林里到处藏着恐龙，有的恐龙还会喷水，遇到喷水恐龙记得要躲开哦~期间还会穿过一个时空隧道，里面有两个超大的恐龙！
+第三站（11:50）：考拉园
+女孩子大部分都喜欢萌萌的动物，来到考拉园一定会敲开心！这是我们第一次看到这么萌的圆滚滚，光是盯着它们睡觉就能笑很久，还有一个看点就是看考拉吃树叶，吧唧吧唧吧唧的样子真香~连我都不由吞了下口水，额额，有点饿了！
+第四站（12:10）：熊猫乐园
+除了可耐的考拉，还有男女通杀的大熊猫！简直迈不开脚步舍不得离开！天哪这个世界上怎么会有滚滚这么可爱的生物呢？看我迷离的眼神，身旁的TA说没见过你这么宠溺地看过我呢~除了三胞胎，还有其他团子，都是一副懒洋洋的样子，超级萌！
+第五站（12:30）：熊猫餐厅
+刚好到了午饭时间，熊猫乐园旁边的熊猫餐厅就是一个解决午餐的好地方，因为可以和熊猫双胞胎亲亲爱爱一起吃午饭，而且套餐价格也还可以接受，七八十元起。吃完午餐可以看一看亲亲爱爱，这两只小家伙一直在打架，从树上打到树下，打的不亦乐乎，看的人也不亦乐乎！像极了平时一起打打闹闹的我们哈哈哈哈！
+第六站（14:00）：4D影院
+熊猫餐厅周边还有4D影院，刚好可以看看4D电影午休一下，顺便来一场跟平时不一样的电影约会哦~我们两个大孩子看得津津有味，4D的体验还是很神奇的，天上会飘下泡泡，打斗的剧情椅子还会跟着摇摆，有点刺激！
+第七站（15:00）：亚洲象园
+休息了一下，我们就要去喂大象啦！大象的口粮是香蕉，30元/五根！不知道是不是我的错觉，我感觉吃了香蕉的大象咧开嘴在微笑嘻嘻~在这里教大家一个大招，五根香蕉可以掰成十段，就可以喂十次啦！投食当然也是为了跟大象来个近距离合照，来一个不一样的秀恩爱方式~咔嚓！
+第八站（15:30）：长颈鹿广场
+大象旁边就是长颈鹿广场，也是可以投喂的！如果你实在不想花钱，我这里又有一招，那就是等别人在投喂的时候，立马咔嚓拍下长颈鹿跟你们的合照，是不是超级聪明哒！不过看长颈鹿的时候可要注意不要太近哦，不然可能会被长颈鹿的口水滴到哦~
+第九站（16:00）：空中缆车
+这个时候感觉已经走了好久好久，是时候休息一下了，于是空中缆车走起！空中缆车有两条路线：环园线和天鹅湖线！重点还是免费哦！这票价真的值了！
+天鹅湖线
+天鹅湖线是从熊猫乐园站——天鹅湖站的路线，缆车将低空横跨天鹅湖和鸳鸯湖，在缆车上俯瞰整个天鹅湖！听说天鹅一生严守一夫一妻制，若一方死亡，另一方则不食不眠，一意殉情！所以天鹅被视为忠诚和永恒爱情的象征。所以情侣们当然要来沾沾天鹅的美好祝愿~成双成对的天鹅，还有白鹭、海鸥等湖居动物朋友扑腾翅膀溅起水花，伴随湖风习习，真的是很舒服。
+环园线
+建议大家坐环园线，也就是从熊猫乐园站——东非草原站——天鹅湖站——熊猫乐园站！整个路程大概30分钟，低空掠过整个园区时可以再看一遍动物，可以看到在奔腾的长颈鹿、跳羚、斑马等，还可以从空中看到考拉馆和熊猫乐园，记得跟住在半空中的团子们say hi哦！刚好是傍晚时分，可以跟最爱的人一起在夕阳下来张合照，简直不要太浪漫~
+第十站（17:00）：看火烈鸟
+坐完空中缆车，已经快到闭园时间啦！沿着路标往南门走，路上还能相遇很多小动物，其中就有风靡时尚圈的火烈鸟！红红火火真的是太耀眼了，有红的白的，太美了！看着看着旁边的傻货突然神秘兮兮地问我你知道为什么火烈鸟有的是白色有的是红色吗？“不知道哇”“那我就勉为其难地跟你科普一下”然后巴拉巴拉讲了一通之后：怎么样，现在是不是觉得本公子特别博学~看来是做足了功课额！
+第十一站（17:30）：南门纪念品商场
 看了这么多萌萌的动物，肯定想把可爱的动物带回家！最后可以到南门的纪念品商场逛一逛，各自为对方选购精美可爱的动物玩具和礼品，在带走和动物们的美丽回忆的同时，把动物玩具带回家，以后看到这些可爱的小玩意就会想起这段美好记忆呢！</t>
         </is>
       </c>
       <c r="M3" s="5" t="n">
-        <v>5426</v>
+        <v>2159</v>
       </c>
       <c r="N3" s="5" t="n">
         <v>2153</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>0.613</v>
+        <v>0.003</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="5" t="n">
         <v>5</v>
@@ -1306,176 +1159,83 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;广州长隆欢乐世界游玩攻略&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;【交通指南】&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;因为当天晚上要入住广州长隆熊猫酒店，所以我们先前往酒店寄存行李！在地铁7号线汉溪长隆地铁站E出口，可直接乘坐免费巴士到达长隆熊猫酒店，到达酒店先前往一楼酒店大堂服务中心寄存行李。从广州长隆熊猫酒店出发步行至广州长隆欢乐世界北门，几分钟即可到达，散散步当放松也不错～&lt;/div&gt;
-&lt;div class="text p"&gt; &lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;关于安检入园：&lt;/strong&gt;为保证公众安全，进入长隆各主题公园及马戏表演场馆的游客（观众）必须接受安全检查，请您主动打开随身包裹配合安全检查，严禁携带管制器具、枪支弹药、易燃易爆等物品以及法律法规规定的其它违禁物品入园（场）。&lt;br/&gt;
- &lt;/div&gt;
-&lt;div class="text p"&gt;从北门进的话第一站就是尖叫地带啦，我们将在这里开启尖叫路线，为广州长隆欢乐世界之旅开一个好头～Follow me～&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;上午——尖叫地带&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;推荐指数：※※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;火箭过山车 尖叫指数：※※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="list-img-wrap"&gt;
-&lt;ul class="row list-img"&gt;&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt; &lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt; &lt;/div&gt;
-&lt;/li&gt;
-&lt;/ul&gt;&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;来广州长隆欢乐世界一定要打卡的就是过山车了！虽然有很多过山车，但是每一种的体验都是不一样的，火箭过山车能够让你们一次性体验“垂直跌落”、“倒挂俯冲”和“高速回旋”～当然更是显示你男友力的最好时刻，要记得全程紧握着她的手，紧张时陪她一起放声大叫，以后回想起来也是专属于两人的美好回忆呢~但是…我全程都是紧握着自己的手哈哈哈，觉得自己抱紧自己安全点～&lt;/div&gt;
-&lt;div class="text p" style="text-align:center;"&gt;&lt;img alt="419b80377d645862.jpg" class="img-responsive" src="https://cdn.chimelong.com/upload/83379e71244ea9a9/419b80377d645862.jpg" title="image"/&gt;&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt; &lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="list-img-wrap"&gt; &lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;龙卷风暴 尖叫指数：※※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/assets/images/ljfb1.6eec923.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;中午：椰林餐厅+欢乐嘉年华&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;推荐指数：※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;在尖叫地带游玩下来其实差不多就饿了哈哈，因为尖叫真的消耗太多能量啦！ 但没关系，园区有多个主题餐厅和美食小站，可以及时帮你补充满满能量，也可以在餐厅内歇歇脚，一起吐槽对方紧张时的大喊大叫～继续体验尖叫设施~&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;椰林餐厅 好吃指数：※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;因为午后想去星梦奇园和欢乐嘉年华溜溜，所以选择的是椰林餐厅，地道的粤式美食滋味咸香鸡和东南亚风味的泰式风情沙拉菜式，让您吃的生态，品的自然。还有现烤的正宗德克萨斯牛柳焦香味浓，肉质鲜嫩，一定会让您垂涎欲滴！ ～还有其他风格的餐厅以后还要再去试试～&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="" class="list-img img-responsive" src="https://cdn.chimelong.com/upload/17189bc3c67f1bb8/3930f1515ca1919d.jpg"/&gt;&lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;因为午饭后不宜进行剧烈运动，我们就到了星梦奇园区域，我们成为饭后缓冲地带哈哈，开启童真线路～但其实虽然是叫欢乐嘉年华，但也是情侣的打卡胜地呢！毕竟谈起恋爱来真的会变小孩子…emmm...我说的是开心得跟小孩子一样啦～&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;梦幻转马 浪漫指数：※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;都说女生心目中都有一个公主梦，那就带她来梦幻转马吧~这个项目可以说是来广州长隆欢乐世界，除了垂直过山车外第二个比打卡的了哈哈，至少在梦幻转马前留下一张甜甜的剪影图也好呀～&lt;/div&gt;
-&lt;div class="text p"&gt;两人一起骑上木马，在马背上旋转、奔腾，进入浪漫又神奇的童话世界～这个项目速度比较缓慢，在中心转轴处也有很多个镜子方便女生用女生拍下美美的照片～在这里男生要记住了，一定要帮女孩子拍一张照片，女孩子不一定会说，但是你要主动点！！我就只能帮你到这了～当然这个项目也有固定的摄影点，不相信自己拍照技术的，就靠园区的摄影师啦～看到镜头时记得一起比心~留下一张甜甜的合影~&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;欢乐跳跳 尖叫指数：※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;在欢乐嘉年华的项目都比较温和，其中欢乐跳跳可以说是自由落体的迷你版，也可以说是自由落体的入门级项目了～有些男生是很怕这种突然的失重感的，女生如果发现了，可以告诉他：没事，你坐中间会好点。安慰安慰他，其实也没有什么区别啦，就是给他一种他身边都有很多人的安全感哈哈~&lt;/div&gt;
-&lt;div class="text p"&gt;在欢乐嘉年华里还有其他小朋友体验的项目，但是谁还不是个孩子呢对吧，拉上你的男朋友一起体验体验呀～&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;欢乐剧场《魔法奇幻之旅》表演 好看指数：※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;在欢乐嘉年华里逛一逛差不多一点多了，看了园区地图，在欢乐剧场会有表演《魔法奇幻之旅》，会表演魔术，还能跟魔术师互动呢，在剧场里歇歇脚也是不错滴～欢乐剧场就在梦幻转马附近，三两分钟左右的路程，赶不及的话也可以再出去溜一溜，然后四点半还会有一场的～对魔术不感兴趣的朋友也往前走，玩一玩，然后观看园区大巡游。&lt;/div&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;img alt="e02941876d4db270.jpg" src="https://cdn.chimelong.com/upload/6568380c5047b676/e02941876d4db270.jpg" title="image"/&gt;&lt;/p&gt;
-&lt;p&gt; &lt;/p&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;在欢乐剧场看完表演后稍继续游玩，就来到了丛林探险和律动天地，又开启了我们的尖叫路线啦～ps.其实往垂直过山车走的路上，我们又体验了一次超级大摆锤哈哈～我感觉急流勇进也挺好玩的，但是有水，男朋友怕鞋子湿了死活不肯去哈哈，男人果然爱鞋如命，想玩的朋友也别担心噢，排队的地方会有雨衣卖滴！&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;下午——律动天地&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;推荐指数：※※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;垂直过山车 尖叫指数：※※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="list-img-wrap"&gt;
-&lt;ul class="row list-img"&gt;&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/czgsc1.393645f.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/czgsc2.1062028.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;/ul&gt;&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;垂直过山车能够让你上天也能够让你入地，我心中也是排名第一的！这个项目真的不分性别，只有勇敢的人才能直接上去体验。如果胆子小在体验前一定要做好心理建设工作，比如先跟对象打预防针：我等下要是叫出来，你可不能笑我！你看别的男生也是有大叫的，所以我大叫的话你也不能笑我！&lt;/div&gt;
-&lt;div class="text p"&gt;此外呢，学霸情侣可以通过转移注意力来缓解紧张，比如两个人跟着过山车的轨迹来分享重力势能和动力势能的互相转换，那么你们的对话大概就是：你看你看往上是XX势能转换为XX势能，下来了，XX势能转换为XX势能～当然啦这也是一个可以让你们心灵相通的项目呀——垂直处悬挂时的紧张，慢速爬升的头皮发麻，快速下落的大声尖叫，这些奇妙的内心活动，让你们此时此刻心灵相通！&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;超级大摆锤 尖叫指数：※※※※&lt;/strong&gt;&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="list-img-wrap"&gt;
-&lt;ul class="row list-img"&gt;&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/cjdbc1.99578e7.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/cjdbc2.65d4f90.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;/ul&gt;&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;刚从垂直过山车下下来，有没有边走边意犹未尽？当当当当，超级大摆锤正在你面前甩起来呢～超级大摆锤不仅左右旋转还上下摇摆，360度无死角翻转，所以记得把贵重物品放在物品存储柜噢，避免被甩飞了。当然时不时也会发生鞋子被甩飞的事情，所以鞋带也要记得系紧啦哈哈！当超级大摆锤往上摆的时候，你可以张开双手拥抱天空，假装自己就要上天了，浪漫的你也可以牵着她的手，在最高点的时候告诉她，走吧，我们一起私奔到月球～？整个路线游玩下来可能大概四点多五点左右，时间上允许的话还是推荐再看一场演出，对，但是我们赶着去吃晚饭就提前出园啦～&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;&lt;strong&gt;关于纪念品&lt;/strong&gt;&lt;/div&gt;
-&lt;div class="text p"&gt;一路这样玩下来，其实我们已经慢慢地从北门走到了接近南门的地方，因为我们还要回到酒店，从北门出比较方便，所以我们就往回走，顺便再体验一次你喜欢的项目嘿嘿～而且一般旅程下来，吃吃玩玩，但是感觉还差点什么？没错！那就是买点纪念品，养成旅游留下纪念品这样的仪式感，就会有两个人一起去过很多地方的感觉～&lt;/div&gt;
-&lt;div class="text p"&gt;因为南门出口缤纷店设了闸，进店就意味着出园，我们按打算是从北门出滴，所以就没有在那买纪念品了，但是如果想从南门出，坐地铁的话，超方便的！除了南门出口缤纷店，园区内有多处纪念品商店，放眼望去尽是卡卡虎、鲸鲨、企鹅、魔鬼鱼等长隆集团明星的系列商品，我们就在往回走的路上逛了一逛，在五花八门的可爱商品中，为对方挑选礼物吧~也可以男生买卡卡的，女生买琦琦的，这样也是情侣款呢～&lt;/div&gt;
-&lt;/div&gt;
-&lt;div class="list-img-wrap"&gt;
-&lt;ul class="row list-img"&gt;&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/gyjnp1.45b82fa.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/gyjnp2.06b862a.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/gyjnp3.2f7c078.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;li class="col-sm-6"&gt;
-&lt;div class="oImg"&gt;&lt;img alt="" src="https://cdn.chimelong.com/assets/images/gyjnp4.7d2454b.jpg"/&gt;&lt;/div&gt;
-&lt;/li&gt;
-&lt;/ul&gt;&lt;/div&gt;
-&lt;div class="text-wrap"&gt;
-&lt;div class="text p"&gt;游完长隆欢乐世界，从北门出园，旁边正是我们的下一站：广州长隆国际大马戏！ 这个时间点出园最大的好处就是可以慢悠悠地去广州长隆国际大马戏吃个晚饭，还有占个好位置！&lt;/div&gt;
-&lt;div class="text p"&gt; &lt;/div&gt;
-&lt;div class="text p"&gt; &lt;/div&gt;
-&lt;div class="text p"&gt; &lt;/div&gt;
-&lt;/div&gt;
-&lt;/div&gt; </t>
+          <t>广州长隆欢乐世界游玩攻略
+【交通指南】
+因为当天晚上要入住广州长隆熊猫酒店，所以我们先前往酒店寄存行李！在地铁7号线汉溪长隆地铁站E出口，可直接乘坐免费巴士到达长隆熊猫酒店，到达酒店先前往一楼酒店大堂服务中心寄存行李。从广州长隆熊猫酒店出发步行至广州长隆欢乐世界北门，几分钟即可到达，散散步当放松也不错～
+关于安检入园：为保证公众安全，进入长隆各主题公园及马戏表演场馆的游客（观众）必须接受安全检查，请您主动打开随身包裹配合安全检查，严禁携带管制器具、枪支弹药、易燃易爆等物品以及法律法规规定的其它违禁物品入园（场）。
+从北门进的话第一站就是尖叫地带啦，我们将在这里开启尖叫路线，为广州长隆欢乐世界之旅开一个好头～Follow me～
+上午——尖叫地带
+推荐指数：※※※※※
+火箭过山车 尖叫指数：※※※※※
+来广州长隆欢乐世界一定要打卡的就是过山车了！虽然有很多过山车，但是每一种的体验都是不一样的，火箭过山车能够让你们一次性体验“垂直跌落”、“倒挂俯冲”和“高速回旋”～当然更是显示你男友力的最好时刻，要记得全程紧握着她的手，紧张时陪她一起放声大叫，以后回想起来也是专属于两人的美好回忆呢~但是…我全程都是紧握着自己的手哈哈哈，觉得自己抱紧自己安全点～
+龙卷风暴 尖叫指数：※※※※※
+中午：椰林餐厅+欢乐嘉年华
+推荐指数：※※※※
+在尖叫地带游玩下来其实差不多就饿了哈哈，因为尖叫真的消耗太多能量啦！ 但没关系，园区有多个主题餐厅和美食小站，可以及时帮你补充满满能量，也可以在餐厅内歇歇脚，一起吐槽对方紧张时的大喊大叫～继续体验尖叫设施~
+椰林餐厅 好吃指数：※※※※
+因为午后想去星梦奇园和欢乐嘉年华溜溜，所以选择的是椰林餐厅，地道的粤式美食滋味咸香鸡和东南亚风味的泰式风情沙拉菜式，让您吃的生态，品的自然。还有现烤的正宗德克萨斯牛柳焦香味浓，肉质鲜嫩，一定会让您垂涎欲滴！ ～还有其他风格的餐厅以后还要再去试试～
+因为午饭后不宜进行剧烈运动，我们就到了星梦奇园区域，我们成为饭后缓冲地带哈哈，开启童真线路～但其实虽然是叫欢乐嘉年华，但也是情侣的打卡胜地呢！毕竟谈起恋爱来真的会变小孩子…emmm...我说的是开心得跟小孩子一样啦～
+梦幻转马 浪漫指数：※※※※
+都说女生心目中都有一个公主梦，那就带她来梦幻转马吧~这个项目可以说是来广州长隆欢乐世界，除了垂直过山车外第二个比打卡的了哈哈，至少在梦幻转马前留下一张甜甜的剪影图也好呀～
+两人一起骑上木马，在马背上旋转、奔腾，进入浪漫又神奇的童话世界～这个项目速度比较缓慢，在中心转轴处也有很多个镜子方便女生用女生拍下美美的照片～在这里男生要记住了，一定要帮女孩子拍一张照片，女孩子不一定会说，但是你要主动点！！我就只能帮你到这了～当然这个项目也有固定的摄影点，不相信自己拍照技术的，就靠园区的摄影师啦～看到镜头时记得一起比心~留下一张甜甜的合影~
+欢乐跳跳 尖叫指数：※※※※
+在欢乐嘉年华的项目都比较温和，其中欢乐跳跳可以说是自由落体的迷你版，也可以说是自由落体的入门级项目了～有些男生是很怕这种突然的失重感的，女生如果发现了，可以告诉他：没事，你坐中间会好点。安慰安慰他，其实也没有什么区别啦，就是给他一种他身边都有很多人的安全感哈哈~
+在欢乐嘉年华里还有其他小朋友体验的项目，但是谁还不是个孩子呢对吧，拉上你的男朋友一起体验体验呀～
+欢乐剧场《魔法奇幻之旅》表演 好看指数：※※※※
+在欢乐嘉年华里逛一逛差不多一点多了，看了园区地图，在欢乐剧场会有表演《魔法奇幻之旅》，会表演魔术，还能跟魔术师互动呢，在剧场里歇歇脚也是不错滴～欢乐剧场就在梦幻转马附近，三两分钟左右的路程，赶不及的话也可以再出去溜一溜，然后四点半还会有一场的～对魔术不感兴趣的朋友也往前走，玩一玩，然后观看园区大巡游。
+在欢乐剧场看完表演后稍继续游玩，就来到了丛林探险和律动天地，又开启了我们的尖叫路线啦～ps.其实往垂直过山车走的路上，我们又体验了一次超级大摆锤哈哈～我感觉急流勇进也挺好玩的，但是有水，男朋友怕鞋子湿了死活不肯去哈哈，男人果然爱鞋如命，想玩的朋友也别担心噢，排队的地方会有雨衣卖滴！
+下午——律动天地
+推荐指数：※※※※※
+垂直过山车 尖叫指数：※※※※※
+垂直过山车能够让你上天也能够让你入地，我心中也是排名第一的！这个项目真的不分性别，只有勇敢的人才能直接上去体验。如果胆子小在体验前一定要做好心理建设工作，比如先跟对象打预防针：我等下要是叫出来，你可不能笑我！你看别的男生也是有大叫的，所以我大叫的话你也不能笑我！
+此外呢，学霸情侣可以通过转移注意力来缓解紧张，比如两个人跟着过山车的轨迹来分享重力势能和动力势能的互相转换，那么你们的对话大概就是：你看你看往上是XX势能转换为XX势能，下来了，XX势能转换为XX势能～当然啦这也是一个可以让你们心灵相通的项目呀——垂直处悬挂时的紧张，慢速爬升的头皮发麻，快速下落的大声尖叫，这些奇妙的内心活动，让你们此时此刻心灵相通！
+超级大摆锤 尖叫指数：※※※※
+刚从垂直过山车下下来，有没有边走边意犹未尽？当当当当，超级大摆锤正在你面前甩起来呢～超级大摆锤不仅左右旋转还上下摇摆，360度无死角翻转，所以记得把贵重物品放在物品存储柜噢，避免被甩飞了。当然时不时也会发生鞋子被甩飞的事情，所以鞋带也要记得系紧啦哈哈！当超级大摆锤往上摆的时候，你可以张开双手拥抱天空，假装自己就要上天了，浪漫的你也可以牵着她的手，在最高点的时候告诉她，走吧，我们一起私奔到月球～？整个路线游玩下来可能大概四点多五点左右，时间上允许的话还是推荐再看一场演出，对，但是我们赶着去吃晚饭就提前出园啦～
+关于纪念品
+一路这样玩下来，其实我们已经慢慢地从北门走到了接近南门的地方，因为我们还要回到酒店，从北门出比较方便，所以我们就往回走，顺便再体验一次你喜欢的项目嘿嘿～而且一般旅程下来，吃吃玩玩，但是感觉还差点什么？没错！那就是买点纪念品，养成旅游留下纪念品这样的仪式感，就会有两个人一起去过很多地方的感觉～
+因为南门出口缤纷店设了闸，进店就意味着出园，我们按打算是从北门出滴，所以就没有在那买纪念品了，但是如果想从南门出，坐地铁的话，超方便的！除了南门出口缤纷店，园区内有多处纪念品商店，放眼望去尽是卡卡虎、鲸鲨、企鹅、魔鬼鱼等长隆集团明星的系列商品，我们就在往回走的路上逛了一逛，在五花八门的可爱商品中，为对方挑选礼物吧~也可以男生买卡卡的，女生买琦琦的，这样也是情侣款呢～
+游完长隆欢乐世界，从北门出园，旁边正是我们的下一站：广州长隆国际大马戏！ 这个时间点出园最大的好处就是可以慢悠悠地去广州长隆国际大马戏吃个晚饭，还有占个好位置！</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>【交通指南】
-因为当天晚上要入住广州长隆熊猫酒店，所以我们先前往酒店寄存行李！在地铁7号线汉溪长隆地铁站E出口，可直接乘坐免费巴士到达长隆熊猫酒店，到达酒店先前往一楼酒店大堂服务中心寄存行李。从广州长隆熊猫酒店出发步行至广州长隆欢乐世界北门，几分钟即可到达，散散步当放松也不错～
-关于安检入园：为保证公众安全，进入长隆各主题公园及马戏表演场馆的游客（观众）必须接受安全检查，请您主动打开随身包裹配合安全检查，严禁携带管制器具、枪支弹药、易燃易爆等物品以及法律法规规定的其它违禁物品入园（场）。
-从北门进的话第一站就是尖叫地带啦，我们将在这里开启尖叫路线，为广州长隆欢乐世界之旅开一个好头～Follow me～
-上午——尖叫地带
-来广州长隆欢乐世界一定要打卡的就是过山车了！虽然有很多过山车，但是每一种的体验都是不一样的，火箭过山车能够让你们一次性体验“垂直跌落”、“倒挂俯冲”和“高速回旋”～当然更是显示你男友力的最好时刻，要记得全程紧握着她的手，紧张时陪她一起放声大叫，以后回想起来也是专属于两人的美好回忆呢~但是…我全程都是紧握着自己的手哈哈哈，觉得自己抱紧自己安全点～
-中午：椰林餐厅+欢乐嘉年华
-在尖叫地带游玩下来其实差不多就饿了哈哈，因为尖叫真的消耗太多能量啦！但没关系，园区有多个主题餐厅和美食小站，可以及时帮你补充满满能量，也可以在餐厅内歇歇脚，一起吐槽对方紧张时的大喊大叫～继续体验尖叫设施~
-因为午后想去星梦奇园和欢乐嘉年华溜溜，所以选择的是椰林餐厅，地道的粤式美食滋味咸香鸡和东南亚风味的泰式风情沙拉菜式，让您吃的生态，品的自然。还有现烤的正宗德克萨斯牛柳焦香味浓，肉质鲜嫩，一定会让您垂涎欲滴！～还有其他风格的餐厅以后还要再去试试～
-因为午饭后不宜进行剧烈运动，我们就到了星梦奇园区域，我们成为饭后缓冲地带哈哈，开启童真线路～但其实虽然是叫欢乐嘉年华，但也是情侣的打卡胜地呢！毕竟谈起恋爱来真的会变小孩子…emmm……我说的是开心得跟小孩子一样啦～
-都说女生心目中都有一个公主梦，那就带她来梦幻转马吧~这个项目可以说是来广州长隆欢乐世界，除了垂直过山车外第二个比打卡的了哈哈，至少在梦幻转马前留下一张甜甜的剪影图也好呀～
-两人一起骑上木马，在马背上旋转、奔腾，进入浪漫又神奇的童话世界～这个项目速度比较缓慢，在中心转轴处也有很多个镜子方便女生用女生拍下美美的照片～在这里男生要记住了，一定要帮女孩子拍一张照片，女孩子不一定会说，但是你要主动点！我就只能帮你到这了～当然这个项目也有固定的摄影点，不相信自己拍照技术的，就靠园区的摄影师啦～看到镜头时记得一起比心~留下一张甜甜的合影~
-在欢乐嘉年华的项目都比较温和，其中欢乐跳跳可以说是自由落体的迷你版，也可以说是自由落体的入门级项目了～有些男生是很怕这种突然的失重感的，女生如果发现了，可以告诉他：没事，你坐中间会好点。安慰安慰他，其实也没有什么区别啦，就是给他一种他身边都有很多人的安全感哈哈~
-在欢乐嘉年华里还有其他小朋友体验的项目，但是谁还不是个孩子呢对吧，拉上你的男朋友一起体验体验呀～
-在欢乐嘉年华里逛一逛差不多一点多了，看了园区地图，在欢乐剧场会有表演《魔法奇幻之旅》，会表演魔术，还能跟魔术师互动呢，在剧场里歇歇脚也是不错滴～欢乐剧场就在梦幻转马附近，三两分钟左右的路程，赶不及的话也可以再出去溜一溜，然后四点半还会有一场的～对魔术不感兴趣的朋友也往前走，玩一玩，然后观看园区大巡游。
-在欢乐剧场看完表演后稍继续游玩，就来到了丛林探险和律动天地，又开启了我们的尖叫路线啦～ps.其实往垂直过山车走的路上，我们又体验了一次超级大摆锤哈哈～我感觉急流勇进也挺好玩的，但是有水，男朋友怕鞋子湿了死活不肯去哈哈，男人果然爱鞋如命，想玩的朋友也别担心噢，排队的地方会有雨衣卖滴！
-下午——律动天地
-垂直过山车能够让你上天也能够让你入地，我心中也是排名第一的！这个项目真的不分性别，只有勇敢的人才能直接上去体验。如果胆子小在体验前一定要做好心理建设工作，比如先跟对象打预防针：我等下要是叫出来，你可不能笑我！你看别的男生也是有大叫的，所以我大叫的话你也不能笑我！
-此外呢，学霸情侣可以通过转移注意力来缓解紧张，比如两个人跟着过山车的轨迹来分享重力势能和动力势能的互相转换，那么你们的对话大概就是：你看你看往上是XX势能转换为XX势能，下来了，XX势能转换为XX势能～当然啦这也是一个可以让你们心灵相通的项目呀——垂直处悬挂时的紧张，慢速爬升的头皮发麻，快速下落的大声尖叫，这些奇妙的内心活动，让你们此时此刻心灵相通！
-刚从垂直过山车下下来，有没有边走边意犹未尽？当当当当，超级大摆锤正在你面前甩起来呢～超级大摆锤不仅左右旋转还上下摇摆，360度无死角翻转，所以记得把贵重物品放在物品存储柜噢，避免被甩飞了。当然时不时也会发生鞋子被甩飞的事情，所以鞋带也要记得系紧啦哈哈！当超级大摆锤往上摆的时候，你可以张开双手拥抱天空，假装自己就要上天了，浪漫的你也可以牵着她的手，在最高点的时候告诉她，走吧，我们一起私奔到月球～？整个路线游玩下来可能大概四点多五点左右，时间上允许的话还是推荐再看一场演出，对，但是我们赶着去吃晚饭就提前出园啦～
-关于纪念品
-一路这样玩下来，其实我们已经慢慢地从北门走到了接近南门的地方，因为我们还要回到酒店，从北门出比较方便，所以我们就往回走，顺便再体验一次你喜欢的项目嘿嘿～而且一般旅程下来，吃吃玩玩，但是感觉还差点什么？没错！那就是买点纪念品，养成旅游留下纪念品这样的仪式感，就会有两个人一起去过很多地方的感觉～
-因为南门出口缤纷店设了闸，进店就意味着出园，我们按打算是从北门出滴，所以就没有在那买纪念品了，但是如果想从南门出，坐地铁的话，超方便的！除了南门出口缤纷店，园区内有多处纪念品商店，放眼望去尽是卡卡虎、鲸鲨、企鹅、魔鬼鱼等长隆集团明星的系列商品，我们就在往回走的路上逛了一逛，在五花八门的可爱商品中，为对方挑选礼物吧~也可以男生买卡卡的，女生买琦琦的，这样也是情侣款呢～
+          <t>【交通指南】
+因为当天晚上要入住广州长隆熊猫酒店，所以我们先前往酒店寄存行李！在地铁7号线汉溪长隆地铁站E出口，可直接乘坐免费巴士到达长隆熊猫酒店，到达酒店先前往一楼酒店大堂服务中心寄存行李。从广州长隆熊猫酒店出发步行至广州长隆欢乐世界北门，几分钟即可到达，散散步当放松也不错～
+关于安检入园：为保证公众安全，进入长隆各主题公园及马戏表演场馆的游客（观众）必须接受安全检查，请您主动打开随身包裹配合安全检查，严禁携带管制器具、枪支弹药、易燃易爆等物品以及法律法规规定的其它违禁物品入园（场）。
+从北门进的话第一站就是尖叫地带啦，我们将在这里开启尖叫路线，为广州长隆欢乐世界之旅开一个好头～Follow me～
+上午——尖叫地带
+来广州长隆欢乐世界一定要打卡的就是过山车了！虽然有很多过山车，但是每一种的体验都是不一样的，火箭过山车能够让你们一次性体验“垂直跌落”、“倒挂俯冲”和“高速回旋”～当然更是显示你男友力的最好时刻，要记得全程紧握着她的手，紧张时陪她一起放声大叫，以后回想起来也是专属于两人的美好回忆呢~但是…我全程都是紧握着自己的手哈哈哈，觉得自己抱紧自己安全点～
+中午：椰林餐厅+欢乐嘉年华
+在尖叫地带游玩下来其实差不多就饿了哈哈，因为尖叫真的消耗太多能量啦！但没关系，园区有多个主题餐厅和美食小站，可以及时帮你补充满满能量，也可以在餐厅内歇歇脚，一起吐槽对方紧张时的大喊大叫～继续体验尖叫设施~
+因为午后想去星梦奇园和欢乐嘉年华溜溜，所以选择的是椰林餐厅，地道的粤式美食滋味咸香鸡和东南亚风味的泰式风情沙拉菜式，让您吃的生态，品的自然。还有现烤的正宗德克萨斯牛柳焦香味浓，肉质鲜嫩，一定会让您垂涎欲滴！～还有其他风格的餐厅以后还要再去试试～
+因为午饭后不宜进行剧烈运动，我们就到了星梦奇园区域，我们成为饭后缓冲地带哈哈，开启童真线路～但其实虽然是叫欢乐嘉年华，但也是情侣的打卡胜地呢！毕竟谈起恋爱来真的会变小孩子…emmm……我说的是开心得跟小孩子一样啦～
+都说女生心目中都有一个公主梦，那就带她来梦幻转马吧~这个项目可以说是来广州长隆欢乐世界，除了垂直过山车外第二个比打卡的了哈哈，至少在梦幻转马前留下一张甜甜的剪影图也好呀～
+两人一起骑上木马，在马背上旋转、奔腾，进入浪漫又神奇的童话世界～这个项目速度比较缓慢，在中心转轴处也有很多个镜子方便女生用女生拍下美美的照片～在这里男生要记住了，一定要帮女孩子拍一张照片，女孩子不一定会说，但是你要主动点！我就只能帮你到这了～当然这个项目也有固定的摄影点，不相信自己拍照技术的，就靠园区的摄影师啦～看到镜头时记得一起比心~留下一张甜甜的合影~
+在欢乐嘉年华的项目都比较温和，其中欢乐跳跳可以说是自由落体的迷你版，也可以说是自由落体的入门级项目了～有些男生是很怕这种突然的失重感的，女生如果发现了，可以告诉他：没事，你坐中间会好点。安慰安慰他，其实也没有什么区别啦，就是给他一种他身边都有很多人的安全感哈哈~
+在欢乐嘉年华里还有其他小朋友体验的项目，但是谁还不是个孩子呢对吧，拉上你的男朋友一起体验体验呀～
+在欢乐嘉年华里逛一逛差不多一点多了，看了园区地图，在欢乐剧场会有表演《魔法奇幻之旅》，会表演魔术，还能跟魔术师互动呢，在剧场里歇歇脚也是不错滴～欢乐剧场就在梦幻转马附近，三两分钟左右的路程，赶不及的话也可以再出去溜一溜，然后四点半还会有一场的～对魔术不感兴趣的朋友也往前走，玩一玩，然后观看园区大巡游。
+在欢乐剧场看完表演后稍继续游玩，就来到了丛林探险和律动天地，又开启了我们的尖叫路线啦～ps.其实往垂直过山车走的路上，我们又体验了一次超级大摆锤哈哈～我感觉急流勇进也挺好玩的，但是有水，男朋友怕鞋子湿了死活不肯去哈哈，男人果然爱鞋如命，想玩的朋友也别担心噢，排队的地方会有雨衣卖滴！
+下午——律动天地
+垂直过山车能够让你上天也能够让你入地，我心中也是排名第一的！这个项目真的不分性别，只有勇敢的人才能直接上去体验。如果胆子小在体验前一定要做好心理建设工作，比如先跟对象打预防针：我等下要是叫出来，你可不能笑我！你看别的男生也是有大叫的，所以我大叫的话你也不能笑我！
+此外呢，学霸情侣可以通过转移注意力来缓解紧张，比如两个人跟着过山车的轨迹来分享重力势能和动力势能的互相转换，那么你们的对话大概就是：你看你看往上是XX势能转换为XX势能，下来了，XX势能转换为XX势能～当然啦这也是一个可以让你们心灵相通的项目呀——垂直处悬挂时的紧张，慢速爬升的头皮发麻，快速下落的大声尖叫，这些奇妙的内心活动，让你们此时此刻心灵相通！
+刚从垂直过山车下下来，有没有边走边意犹未尽？当当当当，超级大摆锤正在你面前甩起来呢～超级大摆锤不仅左右旋转还上下摇摆，360度无死角翻转，所以记得把贵重物品放在物品存储柜噢，避免被甩飞了。当然时不时也会发生鞋子被甩飞的事情，所以鞋带也要记得系紧啦哈哈！当超级大摆锤往上摆的时候，你可以张开双手拥抱天空，假装自己就要上天了，浪漫的你也可以牵着她的手，在最高点的时候告诉她，走吧，我们一起私奔到月球～？整个路线游玩下来可能大概四点多五点左右，时间上允许的话还是推荐再看一场演出，对，但是我们赶着去吃晚饭就提前出园啦～
+关于纪念品
+一路这样玩下来，其实我们已经慢慢地从北门走到了接近南门的地方，因为我们还要回到酒店，从北门出比较方便，所以我们就往回走，顺便再体验一次你喜欢的项目嘿嘿～而且一般旅程下来，吃吃玩玩，但是感觉还差点什么？没错！那就是买点纪念品，养成旅游留下纪念品这样的仪式感，就会有两个人一起去过很多地方的感觉～
+因为南门出口缤纷店设了闸，进店就意味着出园，我们按打算是从北门出滴，所以就没有在那买纪念品了，但是如果想从南门出，坐地铁的话，超方便的！除了南门出口缤纷店，园区内有多处纪念品商店，放眼望去尽是卡卡虎、鲸鲨、企鹅、魔鬼鱼等长隆集团明星的系列商品，我们就在往回走的路上逛了一逛，在五花八门的可爱商品中，为对方挑选礼物吧~也可以男生买卡卡的，女生买琦琦的，这样也是情侣款呢～
 游完长隆欢乐世界，从北门出园，旁边正是我们的下一站：广州长隆国际大马戏！这个时间点出园最大的好处就是可以慢悠悠地去广州长隆国际大马戏吃个晚饭，还有占个好位置！</t>
         </is>
       </c>
       <c r="M4" s="5" t="n">
-        <v>6516</v>
+        <v>2708</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>2545</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>0.624</v>
+        <v>0.06</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>104</v>
+        <v>12</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1550,88 +1310,88 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>五一長隆歡樂世界保姆級攻略｜避開人潮玩回票價！
-
-cortexezu6yn4xgma0分享的 長隆歡樂世界 Trip Moment
-30 天前發布，幫助了 108 位旅客的旅程
-還有另外 357 篇關於 長隆歡樂世界 的 Trip Moment，可為您的旅程提供更多參考
-2026.10.28 長隆歡樂世界即時旅遊資訊
-今日天氣：21~30℃
-今日營業狀態：營業中 | 10:00–22:00 營業 (於 20:00 停售門票)
-點評分：4.7/5 | 28068 評論 | TWD1156起 | 3178位旅客感興趣
-姊妹們快看!五一去長隆歡樂世界必看這份超詳細攻略💯親測有效,一天刷遍所有王牌項目真的太爽啦!🔥
-📅 行程安排(黃金6小時衝關版)
-⏰8:30前
-一定要在北門排隊‼️
-9點開園直接衝鴨!🏃‍♀️
-🎢9:00-12:00 刺激項目黃金時段
-✔️首衝"超級激流"(全球首個旋轉式雙提升系統!全新體驗!)
-✔️接著玩"彈射過山車"(推背感炸裂💥)
-✔️"超級海盜船"(搖擺幅度超大!)
-✔️"U型滑板"(360度旋轉絕了)
-✔️最後體驗"超級大擺錘"和"飛虎跳"
-(這幾個項目中午後排隊都超久)
-🍱12:00-13:30 錯峰午餐+拍美照
-✨推薦南國茶餐廳吃正宗的廣式燒味飯
-✨奇妙島隨便拍都出片
-✨12:45觀看超級可愛的卡通巡遊
-👨‍👩‍👧‍👦13:30-17:30 沉浸體驗+親子時間
-✅星際決戰(4D動感影院超震撼)
-✅歡樂水花戲水區(小朋友最愛)
-✅動物王國餵長頸鹿🦒+看鸚鵡表演
-✅四維影院或魔幻劇場(玩累了正好休息)
-🌈五一專屬彩蛋:
-今年"春日暢玩季"主題活動美哭❗️
-"悅己→熱戀→童夢"三階情感體驗✨
-場景佈置夢幻到炸,拍照絕絕子📸
-全新"超級激流"設備已經開放🎢
-融合卡卡虎IP故事,沉浸感MAX💯
-(十環和垂直過山車在升級中,期待王者歸來👑)
-🚗出行小貼士:
-🔸手機購票:提前在"長隆旅遊"微信買票立省20元
-🔸必備APP:實時查看排隊時間、演出安排,優速卡解決排隊煩惱
-🔸交通建議:3號線漢溪長隆站D出口直達最靠譜
-🔸穿衣指南:運動鞋必備+掛繩手機殼+防曬裝備
-🔸住宿福利:住長隆酒店/熊貓酒店可提前30分鐘入園
+          <t>五一長隆歡樂世界保姆級攻略｜避開人潮玩回票價！
+
+cortexezu6yn4xgma0分享的 長隆歡樂世界 Trip Moment
+30 天前發布，幫助了 108 位旅客的旅程
+還有另外 357 篇關於 長隆歡樂世界 的 Trip Moment，可為您的旅程提供更多參考
+2026.10.28 長隆歡樂世界即時旅遊資訊
+今日天氣：21~30℃
+今日營業狀態：營業中 | 10:00–22:00 營業 (於 20:00 停售門票)
+點評分：4.7/5 | 28068 評論 | TWD1156起 | 3178位旅客感興趣
+姊妹們快看!五一去長隆歡樂世界必看這份超詳細攻略💯親測有效,一天刷遍所有王牌項目真的太爽啦!🔥
+📅 行程安排(黃金6小時衝關版)
+⏰8:30前
+一定要在北門排隊‼️
+9點開園直接衝鴨!🏃‍♀️
+🎢9:00-12:00 刺激項目黃金時段
+✔️首衝"超級激流"(全球首個旋轉式雙提升系統!全新體驗!)
+✔️接著玩"彈射過山車"(推背感炸裂💥)
+✔️"超級海盜船"(搖擺幅度超大!)
+✔️"U型滑板"(360度旋轉絕了)
+✔️最後體驗"超級大擺錘"和"飛虎跳"
+(這幾個項目中午後排隊都超久)
+🍱12:00-13:30 錯峰午餐+拍美照
+✨推薦南國茶餐廳吃正宗的廣式燒味飯
+✨奇妙島隨便拍都出片
+✨12:45觀看超級可愛的卡通巡遊
+👨‍👩‍👧‍👦13:30-17:30 沉浸體驗+親子時間
+✅星際決戰(4D動感影院超震撼)
+✅歡樂水花戲水區(小朋友最愛)
+✅動物王國餵長頸鹿🦒+看鸚鵡表演
+✅四維影院或魔幻劇場(玩累了正好休息)
+🌈五一專屬彩蛋:
+今年"春日暢玩季"主題活動美哭❗️
+"悅己→熱戀→童夢"三階情感體驗✨
+場景佈置夢幻到炸,拍照絕絕子📸
+全新"超級激流"設備已經開放🎢
+融合卡卡虎IP故事,沉浸感MAX💯
+(十環和垂直過山車在升級中,期待王者歸來👑)
+🚗出行小貼士:
+🔸手機購票:提前在"長隆旅遊"微信買票立省20元
+🔸必備APP:實時查看排隊時間、演出安排,優速卡解決排隊煩惱
+🔸交通建議:3號線漢溪長隆站D出口直達最靠譜
+🔸穿衣指南:運動鞋必備+掛繩手機殼+防曬裝備
+🔸住宿福利:住長隆酒店/熊貓酒店可提前30分鐘入園
 五一期間人流量超大❗️建議7:30就要到北門排隊哦~帶上這份攻略,分分鐘值回票價!💕</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>姊妹们快看！五一去长隆欢乐世界必看这份超详细攻略亲测有效，一天刷遍所有王牌项目真的太爽啦！
-行程安排（黄金6小时冲关版）
-8:30前
-一定要在北门排队
-9点开园直接冲鸭！
-9:00-12:00 刺激项目黄金时段
-首冲“超级激流”（全球首个旋转式双提升系统！全新体验！）
-接著玩“弹射过山车”（推背感炸裂）
-“超级海盗船”（摇摆幅度超大！）
-“U型滑板”（360度旋转绝了）
-最后体验“超级大摆锤”和“飞虎跳”
-（这几个项目中午后排队都超久）
-12:00-13:30 错峰午餐+拍美照
-推荐南国茶餐厅吃正宗的广式烧味饭
-奇妙岛随便拍都出片
-12:45观看超级可爱的卡通巡游
-13:30-17:30 沉浸体验+亲子时间
-星际决战（4D动感影院超震撼）
-欢乐水花戏水区（小朋友最爱）
-动物王国喂长颈鹿+看鹦鹉表演
-四维影院或魔幻剧场（玩累了正好休息）
-五一专属彩蛋
-今年“春日畅玩季”主题活动美哭
-“悦己→热恋→童梦”三阶情感体验
-场景布置梦幻到炸，拍照绝绝子
-全新“超级激流”设备已经开放
-融合卡卡虎IP故事，沉浸感MAX
-（十环和垂直过山车在升级中，期待王者归来）
-出行小贴士
-手机购票：提前在“长隆旅游”微信买票立省20元
-必备APP:实时查看排队时间、演出安排，优速卡解决排队烦恼
-交通建议：3号线汉溪长隆站D出口直达最靠谱
-穿衣指南：运动鞋必备+挂绳手机壳+防晒装备
-住宿福利：住长隆酒店/熊猫酒店可提前30分钟入园
+          <t>姊妹们快看！五一去长隆欢乐世界必看这份超详细攻略亲测有效，一天刷遍所有王牌项目真的太爽啦！
+行程安排（黄金6小时冲关版）
+8:30前
+一定要在北门排队
+9点开园直接冲鸭！
+9:00-12:00 刺激项目黄金时段
+首冲“超级激流”（全球首个旋转式双提升系统！全新体验！）
+接著玩“弹射过山车”（推背感炸裂）
+“超级海盗船”（摇摆幅度超大！）
+“U型滑板”（360度旋转绝了）
+最后体验“超级大摆锤”和“飞虎跳”
+（这几个项目中午后排队都超久）
+12:00-13:30 错峰午餐+拍美照
+推荐南国茶餐厅吃正宗的广式烧味饭
+奇妙岛随便拍都出片
+12:45观看超级可爱的卡通巡游
+13:30-17:30 沉浸体验+亲子时间
+星际决战（4D动感影院超震撼）
+欢乐水花戏水区（小朋友最爱）
+动物王国喂长颈鹿+看鹦鹉表演
+四维影院或魔幻剧场（玩累了正好休息）
+五一专属彩蛋
+今年“春日畅玩季”主题活动美哭
+“悦己→热恋→童梦”三阶情感体验
+场景布置梦幻到炸，拍照绝绝子
+全新“超级激流”设备已经开放
+融合卡卡虎IP故事，沉浸感MAX
+（十环和垂直过山车在升级中，期待王者归来）
+出行小贴士
+手机购票：提前在“长隆旅游”微信买票立省20元
+必备APP:实时查看排队时间、演出安排，优速卡解决排队烦恼
+交通建议：3号线汉溪长隆站D出口直达最靠谱
+穿衣指南：运动鞋必备+挂绳手机壳+防晒装备
+住宿福利：住长隆酒店/熊猫酒店可提前30分钟入园
 五一期间人流量超大建议7:30就要到北门排队哦~带上这份攻略，分分钟值回票价！</t>
         </is>
       </c>
@@ -1642,7 +1402,7 @@
         <v>613</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>0.335</v>
+        <v>0.316</v>
       </c>
       <c r="P5" s="5" t="n">
         <v>9</v>
@@ -1720,79 +1480,79 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>廣州長隆不繞路攻略，新手直接抄作業！
-
-_TI***33分享的 長隆歡樂世界 Trip Moment
-30 天前發布，幫助了 349 位旅客的旅程
-6 位旅客與此 Trip Moment 互動，提供更多真實反饋
-還有另外 357 篇關於 長隆歡樂世界 的 Trip Moment，可為您的旅程提供更多參考
-2026.10.28 長隆歡樂世界即時旅遊資訊
-今日天氣：21~30℃
-今日營業狀態：營業中 | 10:00–22:00 營業 (於 20:00 停售門票)
-點評分：4.7/5 | 28068 評論 | TWD1156起 | 3178位旅客感興趣
-如果你是過山車狂熱愛好者,或者喜歡追求心跳刺激的快感,那廣州長隆歡樂世界絕對是你的“快樂老家”!這份一日遊路線,帶你玩轉全園最刺激的“四大天王”,全程不走回頭路,趕緊繫好安全帶,準備起飛!
-🎢 極限過山車一日遊路線(跟著走,尖叫不停)
-核心思路:進園直奔垂直過山車 ➡️ 順時針刷遍熱門項目 ➡️ 下午看表演/親子時光 ➡️ 晚上看大秀壓軸
-09:00 入園 / 安檢入口
-• 必做: 提前到達!一入園就是宏偉的歡樂世界大門,先拍個照打卡。
-09:20 歡樂主街區
-• 玩法: 進入主街,兩邊是各種商店和餐廳。不用停留太久,熟悉一下方向,直奔下一個目標。
-09. 40 垂直過山車(⭐⭐⭐⭐⭐ 必玩)
-• 玩法: 進園第一站必須是它!90度垂直跌落,全程禁食(會嚇吐),體驗自由落體的極致快感,絕對是華南地區最刺激的過山車!
-10. 30 十環過山車(⭐⭐⭐⭐⭐ 必玩)
-• 玩法: 從垂直過山車出來,步行幾分鐘就能到十環過山車。顧名思義,它有十個翻轉圈,速度與激情並存,玩完這個感覺魂都飛了。
-11. 20 超級大擺錘(⭐⭐⭐⭐ 必玩)
-• 玩法: 繼續順時針走,來到超級大擺錘。坐在上面隨著大盤瘋狂搖擺,最高點180度旋轉,考驗你的心理素質和腰腹力量。
-12. 10 午餐休息區
-• 推薦: 玩了三個重頭項目,體力消耗巨大。可以在附近的餐廳(比如“熊貓餐廳”或“噴泉餐廳”)補充能量,吃點肉壓壓驚。
-13. 10 家庭親子區 / 飛馬家庭過山車
-• 玩法: 如果你帶了小朋友,或者想稍微緩一緩,可以來這裡玩飛馬家庭過山車。節奏相對舒緩,適合全家一起體驗。
-14. 10 歡樂劇場 / 表演區
-• 玩法: 下午可以看看精彩的舞台劇,比如《叢林的故事》,演員們的表演非常賣力,特效也很棒,是個不錯的放鬆時刻。
-15. 30 巡遊主街段 / 主題街區
-• 玩法: 跟著花車巡遊隊伍走,看各種卡通人物和花車從眼前經過,氣氛熱烈,記得和喜歡的角色互動合影。
-19:00 夜場演出 / 返程點
-• 玩法: 一天的狂歡接近尾聲,千萬不要錯過晚上的大秀!燈光、煙花、噴泉、無人機齊上陣,視覺效果震撼,看完再滿意離園。
-💡 遊玩小貼士(特種兵必看)
-1. 心臟不好慎入: 園區的過山車非常刺激,有高血壓、心臟病或容易暈眩的朋友請量力而行。
-2. 下載官方APP: 一定要提前下載“長隆旅遊”APP,實時查看各個項目的排隊時間,靈活調整路線。
-3. 穿搭建議: 建議穿短袖短褲,方便在過山車上活動。女生盡量把頭髮紮起來,避免被風吹亂。
-4. 備好雨衣: 雖然大部分項目在室內,但像“飛馬家庭過山車”等戶外項目可能會遇到小雨,備件一次性雨衣更安心。
-5. 注意防曬: 戶外活動多,紫外線強,塗好防曬霜,戴好墨鏡和帽子。
+          <t>廣州長隆不繞路攻略，新手直接抄作業！
+
+_TI***33分享的 長隆歡樂世界 Trip Moment
+30 天前發布，幫助了 349 位旅客的旅程
+6 位旅客與此 Trip Moment 互動，提供更多真實反饋
+還有另外 357 篇關於 長隆歡樂世界 的 Trip Moment，可為您的旅程提供更多參考
+2026.10.28 長隆歡樂世界即時旅遊資訊
+今日天氣：21~30℃
+今日營業狀態：營業中 | 10:00–22:00 營業 (於 20:00 停售門票)
+點評分：4.7/5 | 28068 評論 | TWD1156起 | 3178位旅客感興趣
+如果你是過山車狂熱愛好者,或者喜歡追求心跳刺激的快感,那廣州長隆歡樂世界絕對是你的“快樂老家”!這份一日遊路線,帶你玩轉全園最刺激的“四大天王”,全程不走回頭路,趕緊繫好安全帶,準備起飛!
+🎢 極限過山車一日遊路線(跟著走,尖叫不停)
+核心思路:進園直奔垂直過山車 ➡️ 順時針刷遍熱門項目 ➡️ 下午看表演/親子時光 ➡️ 晚上看大秀壓軸
+09:00 入園 / 安檢入口
+• 必做: 提前到達!一入園就是宏偉的歡樂世界大門,先拍個照打卡。
+09:20 歡樂主街區
+• 玩法: 進入主街,兩邊是各種商店和餐廳。不用停留太久,熟悉一下方向,直奔下一個目標。
+09. 40 垂直過山車(⭐⭐⭐⭐⭐ 必玩)
+• 玩法: 進園第一站必須是它!90度垂直跌落,全程禁食(會嚇吐),體驗自由落體的極致快感,絕對是華南地區最刺激的過山車!
+10. 30 十環過山車(⭐⭐⭐⭐⭐ 必玩)
+• 玩法: 從垂直過山車出來,步行幾分鐘就能到十環過山車。顧名思義,它有十個翻轉圈,速度與激情並存,玩完這個感覺魂都飛了。
+11. 20 超級大擺錘(⭐⭐⭐⭐ 必玩)
+• 玩法: 繼續順時針走,來到超級大擺錘。坐在上面隨著大盤瘋狂搖擺,最高點180度旋轉,考驗你的心理素質和腰腹力量。
+12. 10 午餐休息區
+• 推薦: 玩了三個重頭項目,體力消耗巨大。可以在附近的餐廳(比如“熊貓餐廳”或“噴泉餐廳”)補充能量,吃點肉壓壓驚。
+13. 10 家庭親子區 / 飛馬家庭過山車
+• 玩法: 如果你帶了小朋友,或者想稍微緩一緩,可以來這裡玩飛馬家庭過山車。節奏相對舒緩,適合全家一起體驗。
+14. 10 歡樂劇場 / 表演區
+• 玩法: 下午可以看看精彩的舞台劇,比如《叢林的故事》,演員們的表演非常賣力,特效也很棒,是個不錯的放鬆時刻。
+15. 30 巡遊主街段 / 主題街區
+• 玩法: 跟著花車巡遊隊伍走,看各種卡通人物和花車從眼前經過,氣氛熱烈,記得和喜歡的角色互動合影。
+19:00 夜場演出 / 返程點
+• 玩法: 一天的狂歡接近尾聲,千萬不要錯過晚上的大秀!燈光、煙花、噴泉、無人機齊上陣,視覺效果震撼,看完再滿意離園。
+💡 遊玩小貼士(特種兵必看)
+1. 心臟不好慎入: 園區的過山車非常刺激,有高血壓、心臟病或容易暈眩的朋友請量力而行。
+2. 下載官方APP: 一定要提前下載“長隆旅遊”APP,實時查看各個項目的排隊時間,靈活調整路線。
+3. 穿搭建議: 建議穿短袖短褲,方便在過山車上活動。女生盡量把頭髮紮起來,避免被風吹亂。
+4. 備好雨衣: 雖然大部分項目在室內,但像“飛馬家庭過山車”等戶外項目可能會遇到小雨,備件一次性雨衣更安心。
+5. 注意防曬: 戶外活動多,紫外線強,塗好防曬霜,戴好墨鏡和帽子。
 祝你在長隆玩得開心,尖叫聲不斷!</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>如果你是过山车狂热爱好者，或者喜欢追求心跳刺激的快感，那广州长隆欢乐世界绝对是你的“快乐老家”！这份一日游路线，带你玩转全园最刺激的“四大天王”，全程不走回头路，赶紧系好安全带，准备起飞！
-极限过山车一日游路线（跟著走，尖叫不停）
-核心思路：进园直奔垂直过山车 → 顺时针刷遍热门项目 → 下午看表演/亲子时光 → 晚上看大秀压轴
-09:00 入园 / 安检入口
-必做： 提前到达！一入园就是宏伟的欢乐世界大门，先拍个照打卡。
-09:20 欢乐主街区
-玩法： 进入主街，两边是各种商店和餐厅。不用停留太久，熟悉一下方向，直奔下一个目标。
-09:40 垂直过山车（必玩）
-玩法： 进园第一站必须是它！90度垂直跌落，全程禁食（会吓吐），体验自由落体的极致快感，绝对是华南地区最刺激的过山车！
-10:30 十环过山车（必玩）
-玩法： 从垂直过山车出来，步行几分钟就能到十环过山车。顾名思义，它有十个翻转圈，速度与激情并存，玩完这个感觉魂都飞了。
-11:20 超级大摆锤（必玩）
-玩法： 继续顺时针走，来到超级大摆锤。坐在上面随著大盘疯狂摇摆，最高点180度旋转，考验你的心理素质和腰腹力量。
-12:10 午餐休息区
-推荐： 玩了三个重头项目，体力消耗巨大。可以在附近的餐厅（比如“熊猫餐厅”或“喷泉餐厅”）补充能量，吃点肉压压惊。
-13:10 家庭亲子区 / 飞马家庭过山车
-玩法： 如果你带了小朋友，或者想稍微缓一缓，可以来这里玩飞马家庭过山车。节奏相对舒缓，适合全家一起体验。
-14:10 欢乐剧场 / 表演区
-玩法： 下午可以看看精彩的舞台剧，比如《丛林的故事》,演员们的表演非常卖力，特效也很棒，是个不错的放松时刻。
-15:30 巡游主街段 / 主题街区
-玩法： 跟著花车巡游队伍走，看各种卡通人物和花车从眼前经过，气氛热烈，记得和喜欢的角色互动合影。
-19:00 夜场演出 / 返程点
-玩法： 一天的狂欢接近尾声，千万不要错过晚上的大秀！灯光、烟花、喷泉、无人机齐上阵，视觉效果震撼，看完再满意离园。
-游玩小贴士（特种兵必看）
-1. 心脏不好慎入： 园区的过山车非常刺激，有高血压、心脏病或容易晕眩的朋友请量力而行。
-2. 下载官方APP: 一定要提前下载“长隆旅游”APP,实时查看各个项目的排队时间，灵活调整路线。
-3. 穿搭建议： 建议穿短袖短裤，方便在过山车上活动。女生尽量把头发扎起来，避免被风吹乱。
-4. 备好雨衣： 虽然大部分项目在室内，但像“飞马家庭过山车”等户外项目可能会遇到小雨，备件一次性雨衣更安心。
-5. 注意防晒： 户外活动多，紫外线强，涂好防晒霜，戴好墨镜和帽子。
+          <t>如果你是过山车狂热爱好者，或者喜欢追求心跳刺激的快感，那广州长隆欢乐世界绝对是你的“快乐老家”！这份一日游路线，带你玩转全园最刺激的“四大天王”，全程不走回头路，赶紧系好安全带，准备起飞！
+极限过山车一日游路线（跟著走，尖叫不停）
+核心思路：进园直奔垂直过山车 → 顺时针刷遍热门项目 → 下午看表演/亲子时光 → 晚上看大秀压轴
+09:00 入园 / 安检入口
+必做： 提前到达！一入园就是宏伟的欢乐世界大门，先拍个照打卡。
+09:20 欢乐主街区
+玩法： 进入主街，两边是各种商店和餐厅。不用停留太久，熟悉一下方向，直奔下一个目标。
+09:40 垂直过山车（必玩）
+玩法： 进园第一站必须是它！90度垂直跌落，全程禁食（会吓吐），体验自由落体的极致快感，绝对是华南地区最刺激的过山车！
+10:30 十环过山车（必玩）
+玩法： 从垂直过山车出来，步行几分钟就能到十环过山车。顾名思义，它有十个翻转圈，速度与激情并存，玩完这个感觉魂都飞了。
+11:20 超级大摆锤（必玩）
+玩法： 继续顺时针走，来到超级大摆锤。坐在上面随著大盘疯狂摇摆，最高点180度旋转，考验你的心理素质和腰腹力量。
+12:10 午餐休息区
+推荐： 玩了三个重头项目，体力消耗巨大。可以在附近的餐厅（比如“熊猫餐厅”或“喷泉餐厅”）补充能量，吃点肉压压惊。
+13:10 家庭亲子区 / 飞马家庭过山车
+玩法： 如果你带了小朋友，或者想稍微缓一缓，可以来这里玩飞马家庭过山车。节奏相对舒缓，适合全家一起体验。
+14:10 欢乐剧场 / 表演区
+玩法： 下午可以看看精彩的舞台剧，比如《丛林的故事》,演员们的表演非常卖力，特效也很棒，是个不错的放松时刻。
+15:30 巡游主街段 / 主题街区
+玩法： 跟著花车巡游队伍走，看各种卡通人物和花车从眼前经过，气氛热烈，记得和喜欢的角色互动合影。
+19:00 夜场演出 / 返程点
+玩法： 一天的狂欢接近尾声，千万不要错过晚上的大秀！灯光、烟花、喷泉、无人机齐上阵，视觉效果震撼，看完再满意离园。
+游玩小贴士（特种兵必看）
+1. 心脏不好慎入： 园区的过山车非常刺激，有高血压、心脏病或容易晕眩的朋友请量力而行。
+2. 下载官方APP: 一定要提前下载“长隆旅游”APP,实时查看各个项目的排队时间，灵活调整路线。
+3. 穿搭建议： 建议穿短袖短裤，方便在过山车上活动。女生尽量把头发扎起来，避免被风吹乱。
+4. 备好雨衣： 虽然大部分项目在室内，但像“飞马家庭过山车”等户外项目可能会遇到小雨，备件一次性雨衣更安心。
+5. 注意防晒： 户外活动多，紫外线强，涂好防晒霜，戴好墨镜和帽子。
 祝你在长隆玩得开心，尖叫声不断！</t>
         </is>
       </c>
@@ -1803,7 +1563,7 @@
         <v>1041</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>0.236</v>
+        <v>0.204</v>
       </c>
       <c r="P6" s="5" t="n">
         <v>10</v>
@@ -1881,87 +1641,87 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>🐼🐨長隆野生動物園 | 無回頭路旅遊指南
-
-_TI***mo分享的 長隆野生動物世界 Trip Moment
-2 天前發布，幫助了 23 位旅客的旅程
-還有另外 1285 篇關於 長隆野生動物世界 的 Trip Moment，可為您的旅程提供更多參考
-2026.10.28 長隆野生動物世界即時旅遊資訊
-今日天氣：21~30℃
-今日營業狀態：今天已休園 | 明日09:30–18:00 營業
-點評分：4.8/5 | 107563 評論 | TWD1462起 | 10505位旅客感興趣
-避開北門旅行團人流,全程不折返,一天打卡全部精華✨
-⏰開園9:30|建議9:20南門排隊
-1. 09:30 南門入園
-進門先打卡火烈鳥(錯過的話最後補也可以),
-順路走到熊森林、黑猩猩。
-2. 10:30 纜車熊貓樂園站【環園纜車】
-這裡可預留時間10.即可排隊提前排隊第一波環園
-✅纜車免費不限次數,環園線一圈大約30分鐘。
-3. 11:00 4D影院 → 花果山 → 金猴王國
-4D影片大約10分鐘,老少皆宜;花果山是花車巡遊起點,可以提前看好下午巡遊時間。金猴王國猴子種類超多,上午最活潑。
-4. 12:00 青龍山+科莫多龍
-侏羅紀風格區域,恐龍模型(這個按需可以不看)科莫多巨蜥打卡
-5. 13:00 百虎山|看【白虎跳水】(必看!)
-白虎跳水半點有演出(13:30/14:30…),提前10分鐘佔位,老虎撲水超震撼,園區王牌節目。
-6. 14:00 天鵝湖站坐【小火車】
-坐纜車到天鵝湖站下車,就是小火車起點!這裡也可提前預留時間排隊
-👉小火車選右側座位,動物大多在右邊,穿越五大洲草原。小火車終點回到北門,再坐纜車返回園區中部。
-7. 15:00 動物幼兒園
-奶萌小羊、小老虎、小猴子,很適合拍照。
-15:30 花車大巡遊(花果山始發)
-提前在花果山道路兩邊佔位置!花車互動,演員會揮手送小禮物,全天最熱鬧項目(時間以入園拿到的當日節目表為準)。
-8. 16:30 百虎山→長頸鹿廣場→考拉園→亞洲象
-長頸鹿可以付費投喂,拍照巨出片;考拉園超多考拉,慢悠悠打卡;亞洲象區域看大象洗澡。
-9. 17:10 長隆大熊貓中心(妹豬)
-看熊貓三胞胎+妹豬,傍晚熊貓會出來活動。
-接著逛騏驥天地、細尾獴、山魈、濕地精靈。
-10. 18:00 火烈鳥區域 → 返回南門,結束出園
-南門出去有接駁車 大家遊玩一天的話 可以等待接駁車接送至園區飯店 or 地鐵
-💡必看貼士
-▫️入園第一件事拿紙質節目單!表演時間當日會微調
-▫️纜車+小火車全部包含在門票內,免費不限次
-▫️自帶水杯,園區多處直飲水,穿舒服運動鞋
-▫️南門車位很少!自駕建議停北門坐接駁車過來
-     與野生動物零距離
+          <t>🐼🐨長隆野生動物園 | 無回頭路旅遊指南
+
+_TI***mo分享的 長隆野生動物世界 Trip Moment
+2 天前發布，幫助了 23 位旅客的旅程
+還有另外 1285 篇關於 長隆野生動物世界 的 Trip Moment，可為您的旅程提供更多參考
+2026.10.28 長隆野生動物世界即時旅遊資訊
+今日天氣：21~30℃
+今日營業狀態：今天已休園 | 明日09:30–18:00 營業
+點評分：4.8/5 | 107563 評論 | TWD1462起 | 10505位旅客感興趣
+避開北門旅行團人流,全程不折返,一天打卡全部精華✨
+⏰開園9:30|建議9:20南門排隊
+1. 09:30 南門入園
+進門先打卡火烈鳥(錯過的話最後補也可以),
+順路走到熊森林、黑猩猩。
+2. 10:30 纜車熊貓樂園站【環園纜車】
+這裡可預留時間10.即可排隊提前排隊第一波環園
+✅纜車免費不限次數,環園線一圈大約30分鐘。
+3. 11:00 4D影院 → 花果山 → 金猴王國
+4D影片大約10分鐘,老少皆宜;花果山是花車巡遊起點,可以提前看好下午巡遊時間。金猴王國猴子種類超多,上午最活潑。
+4. 12:00 青龍山+科莫多龍
+侏羅紀風格區域,恐龍模型(這個按需可以不看)科莫多巨蜥打卡
+5. 13:00 百虎山|看【白虎跳水】(必看!)
+白虎跳水半點有演出(13:30/14:30…),提前10分鐘佔位,老虎撲水超震撼,園區王牌節目。
+6. 14:00 天鵝湖站坐【小火車】
+坐纜車到天鵝湖站下車,就是小火車起點!這裡也可提前預留時間排隊
+👉小火車選右側座位,動物大多在右邊,穿越五大洲草原。小火車終點回到北門,再坐纜車返回園區中部。
+7. 15:00 動物幼兒園
+奶萌小羊、小老虎、小猴子,很適合拍照。
+15:30 花車大巡遊(花果山始發)
+提前在花果山道路兩邊佔位置!花車互動,演員會揮手送小禮物,全天最熱鬧項目(時間以入園拿到的當日節目表為準)。
+8. 16:30 百虎山→長頸鹿廣場→考拉園→亞洲象
+長頸鹿可以付費投喂,拍照巨出片;考拉園超多考拉,慢悠悠打卡;亞洲象區域看大象洗澡。
+9. 17:10 長隆大熊貓中心(妹豬)
+看熊貓三胞胎+妹豬,傍晚熊貓會出來活動。
+接著逛騏驥天地、細尾獴、山魈、濕地精靈。
+10. 18:00 火烈鳥區域 → 返回南門,結束出園
+南門出去有接駁車 大家遊玩一天的話 可以等待接駁車接送至園區飯店 or 地鐵
+💡必看貼士
+▫️入園第一件事拿紙質節目單!表演時間當日會微調
+▫️纜車+小火車全部包含在門票內,免費不限次
+▫️自帶水杯,園區多處直飲水,穿舒服運動鞋
+▫️南門車位很少!自駕建議停北門坐接駁車過來
+與野生動物零距離
 查看原文</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>避开北门旅行团人流，全程不折返，一天打卡全部精华
-开园9:30|建议9:20南门排队
-1. 09:30 南门入园
-进门先打卡火烈鸟（错过的话最后补也可以）
-顺路走到熊森林、黑猩猩。
-2. 10:30 缆车熊猫乐园站【环园缆车】
-这里可预留时间10.即可排队提前排队第一波环园
-缆车免费不限次数，环园线一圈大约30分钟。
-3. 11:00 4D影院 → 花果山 → 金猴王国
-4D影片大约10分钟，老少皆宜；花果山是花车巡游起点，可以提前看好下午巡游时间。金猴王国猴子种类超多，上午最活泼。
-4. 12:00 青龙山+科莫多龙
-侏罗纪风格区域，恐龙模型（这个按需可以不看）科莫多巨蜥打卡
-5. 13:00 百虎山|看【白虎跳水】（必看！）
-白虎跳水半点有演出(13:30/14:30…)，提前10分钟占位，老虎扑水超震撼，园区王牌节目。
-6. 14:00 天鹅湖站坐【小火车】
-坐缆车到天鹅湖站下车，就是小火车起点！这里也可提前预留时间排队
-小火车选右侧座位，动物大多在右边，穿越五大洲草原。小火车终点回到北门，再坐缆车返回园区中部。
-7. 15:00 动物幼儿园
-奶萌小羊、小老虎、小猴子，很适合拍照。
-15:30 花车大巡游（花果山始发）
-提前在花果山道路两边占位置！花车互动，演员会挥手送小礼物，全天最热闹项目（时间以入园拿到的当日节目表为准）。
-8. 16:30 百虎山→长颈鹿广场→考拉园→亚洲象
-长颈鹿可以付费投喂，拍照巨出片；考拉园超多考拉，慢悠悠打卡；亚洲象区域看大象洗澡。
-9. 17:10 长隆大熊猫中心（妹猪）
-看熊猫三胞胎+妹猪，傍晚熊猫会出来活动。
-接著逛骐骥天地、细尾獴、山魈、湿地精灵。
-10. 18:00 火烈鸟区域 → 返回南门，结束出园
-南门出去有接驳车 大家游玩一天的话 可以等待接驳车接送至园区饭店 or 地铁
-必看贴士
-入园第一件事拿纸质节目单！表演时间当日会微调
-缆车+小火车全部包含在门票内，免费不限次
-自带水杯，园区多处直饮水，穿舒服运动鞋
-南门车位很少！自驾建议停北门坐接驳车过来
+          <t>避开北门旅行团人流，全程不折返，一天打卡全部精华
+开园9:30|建议9:20南门排队
+1. 09:30 南门入园
+进门先打卡火烈鸟（错过的话最后补也可以）
+顺路走到熊森林、黑猩猩。
+2. 10:30 缆车熊猫乐园站【环园缆车】
+这里可预留时间10.即可排队提前排队第一波环园
+缆车免费不限次数，环园线一圈大约30分钟。
+3. 11:00 4D影院 → 花果山 → 金猴王国
+4D影片大约10分钟，老少皆宜；花果山是花车巡游起点，可以提前看好下午巡游时间。金猴王国猴子种类超多，上午最活泼。
+4. 12:00 青龙山+科莫多龙
+侏罗纪风格区域，恐龙模型（这个按需可以不看）科莫多巨蜥打卡
+5. 13:00 百虎山|看【白虎跳水】（必看！）
+白虎跳水半点有演出(13:30/14:30…)，提前10分钟占位，老虎扑水超震撼，园区王牌节目。
+6. 14:00 天鹅湖站坐【小火车】
+坐缆车到天鹅湖站下车，就是小火车起点！这里也可提前预留时间排队
+小火车选右侧座位，动物大多在右边，穿越五大洲草原。小火车终点回到北门，再坐缆车返回园区中部。
+7. 15:00 动物幼儿园
+奶萌小羊、小老虎、小猴子，很适合拍照。
+15:30 花车大巡游（花果山始发）
+提前在花果山道路两边占位置！花车互动，演员会挥手送小礼物，全天最热闹项目（时间以入园拿到的当日节目表为准）。
+8. 16:30 百虎山→长颈鹿广场→考拉园→亚洲象
+长颈鹿可以付费投喂，拍照巨出片；考拉园超多考拉，慢悠悠打卡；亚洲象区域看大象洗澡。
+9. 17:10 长隆大熊猫中心（妹猪）
+看熊猫三胞胎+妹猪，傍晚熊猫会出来活动。
+接著逛骐骥天地、细尾獴、山魈、湿地精灵。
+10. 18:00 火烈鸟区域 → 返回南门，结束出园
+南门出去有接驳车 大家游玩一天的话 可以等待接驳车接送至园区饭店 or 地铁
+必看贴士
+入园第一件事拿纸质节目单！表演时间当日会微调
+缆车+小火车全部包含在门票内，免费不限次
+自带水杯，园区多处直饮水，穿舒服运动鞋
+南门车位很少！自驾建议停北门坐接驳车过来
 与野生动物零距离</t>
         </is>
       </c>
@@ -1972,7 +1732,7 @@
         <v>809</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.235</v>
+        <v>0.22</v>
       </c>
       <c r="P7" s="5" t="n">
         <v>10</v>
@@ -2050,109 +1810,109 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>廣東長隆歡樂世界旅遊攻略：高效玩轉華南王牌樂園，快樂不踩坑  作為中國主題樂園的標杆之一，廣州長隆歡
-
-JAYLA GOODWIN分享的 長隆歡樂世界 Trip Moment
-30 天前發布，幫助了 999 位旅客的旅程
-31 位旅客與此 Trip Moment 互動，提供更多真實反饋
-還有另外 357 篇關於 長隆歡樂世界 的 Trip Moment，可為您的旅程提供更多參考
-2026.10.28 長隆歡樂世界即時旅遊資訊
-今日天氣：21~30℃
-今日營業狀態：營業中 | 10:00–22:00 營業 (於 20:00 停售門票)
-點評分：4.7/5 | 28068 評論 | TWD1156起 | 3178位旅客感興趣
-廣東長隆歡樂世界旅遊攻略:高效玩轉華南王牌樂園,快樂不踩坑
-作為中國主題樂園的標杆之一,廣州長隆歡樂世界不是簡單的「過山車集合地」,而是一座融合尖端科技、沉浸敘事與嶺南風情的全天候遊樂綜合體。它佔地2000畝,擁有12大主題區、70餘項機動遊戲及數十場演藝秀,日均客流常破3萬——若無規劃,極易陷入排隊兩小時、遊玩五分鐘的疲憊循環。這份實用攻略,專為追求高效率、低消耗、強體驗的遊客訂製,助你把時間花在心跳上,而非隊尾。
-一. 行前必做三件事:省下3小時,多玩2個項目
-✅ 購票預約:微信公眾號「長隆旅遊」官方購票(比現場便宜約20元),務必提前1天預約入園日期(節假日需搶票);學生/老人/兒童按規則帶證件核驗;
-✅ 下載APP+綁定門票:「長隆旅遊」APP實時查排隊時長、演出時間、地圖導航,開啟「快速通行」功能(部分熱門項目可購優速卡,單次30–50元,推薦「垂直過山車」「十環過山車」必買);
-✅ 裝備精簡清單:穿運動鞋(禁拖鞋、高跟鞋)、帶掛繩手機殼、小腰包(存手機+充電寶+濕巾)、防曬帽+冰袖(園區遮陰少);雙肩包需寄存(入口處免費自助儲物櫃充足)。
-二. 交通住宿:離園越近,快樂越久
-📍地址:廣州市番禺區迎賓路88號(地鐵3號線「漢溪長隆站」D出口直達,出站即見園區拱門)。
-🚌最優抵達方式:
-· 地鐵(首選):市區乘3號線至「漢溪長隆站」,全程免換乘,出閘即入園,避免堵車與停車焦慮;
-· 自駕:導航「長隆歡樂世界停車場」,P1/P2最便利(30元/天),但旺季10點後常滿位,建議早於9:00抵達。
-🏨住宿推薦:
-長隆酒店/熊貓酒店(步行5分鐘):住客享提前30分鐘入園+專屬通道,夜間有煙花導覽,性價比最高;
-周邊經濟型酒店(如7天、如家):價格低,但通勤需打車(約15元),適合預算有限者。
-三. 動線規劃:黃金6小時,玩轉核心精華
-⏰ 推薦入園時間:8:30前到達(9:00開園),直奔北區——此時人最少,項目幾乎不用排隊。
-🔹上午(9:00–12:00):衝刺王牌刺激項
-9:00–9:30:直衝「垂直過山車」(亞洲首台彈射式,0–90km/h僅2秒),用優速卡免排40分鐘;
-9. 30–10:15:「十環過山車」(全球唯一雙環過山車,倒掛360°),緊接「U型滑板」(失重感最強);
-10. 15–11:00:「超級大擺錘」+「飛虎跳」(高空蕩秋千),感受腎上腺素持續飆升。
-🔹中午(12:00–13:30):錯峰休整+特色午餐
-· 避開12:30用餐高峰,12:00先吃「南國茶餐廳」廣式燒味飯(叉燒嫩、例湯鮮);
-· 飯後逛「奇妙島」拍照打卡,看卡通巡遊(12:45開始,路線覆蓋主幹道)。
-🔹下午(13:30–17:30):沉浸體驗+親子友好
-· 13:30–14:30:「星際決戰」(4D動感影院,劇情緊湊不暈眩);
-14. 30–15:30:「歡樂水花」(全齡段戲水區,夏季必玩,備好毛巾);
-15. 30–16:30:「動物王國」互動區:餵長頸鹿、摸羊駝、看鸚鵡表演(16:00場次最佳);
-16. 30–17:30:預留給「四維影院」或「魔幻劇場」(每日僅2–3場,APP查準時間)。
-四. 不可錯過的三大隱藏彩蛋
-🔸 夜場加成:18:00後入園票價半價(限當日),燈光秀+煙花秀(20:00開始)浪漫值拉滿,人流量驟減,摩天輪視野絕佳;
-🔸 美食冷知識:「歡樂餐廳」的榴槤披薩、熊貓酒店的竹筒飯、南國茶餐廳的楊枝甘露冰粉,是本地人私藏榜單;
-🔸 帶娃貼士:嬰兒車可租(50元/天),所有洗手間配母嬰室;「兒童天地」區設施軟包安全,家長可在「奇幻漂流」旁休息亭同步觀景。
-五. 重要提醒:快樂可持續的關鍵
--園內消費偏高(瓶裝水15元、冰淇淋35元),可自帶未開封水和小食(安檢允許);
-演出時間每日微調,務必以APP當日推送為準;
-雨天部分戶外項目暫停,但室內場館照常開放,備好輕便雨衣更從容。
-長隆歡樂世界的終極心法,從來不是「刷完所有項目」,  
-而是:  
-在垂直過山車俯衝時放聲大笑,  
-在摩天輪升至最高點時靜靜看雲,  
-在孩子牽你手跑向旋轉木馬時,  
-忽然想起——  
-原來快樂,一直都很簡單,  
-只是我們太久沒讓它,  
+          <t>廣東長隆歡樂世界旅遊攻略：高效玩轉華南王牌樂園，快樂不踩坑  作為中國主題樂園的標杆之一，廣州長隆歡
+
+JAYLA GOODWIN分享的 長隆歡樂世界 Trip Moment
+30 天前發布，幫助了 999 位旅客的旅程
+31 位旅客與此 Trip Moment 互動，提供更多真實反饋
+還有另外 357 篇關於 長隆歡樂世界 的 Trip Moment，可為您的旅程提供更多參考
+2026.10.28 長隆歡樂世界即時旅遊資訊
+今日天氣：21~30℃
+今日營業狀態：營業中 | 10:00–22:00 營業 (於 20:00 停售門票)
+點評分：4.7/5 | 28068 評論 | TWD1156起 | 3178位旅客感興趣
+廣東長隆歡樂世界旅遊攻略:高效玩轉華南王牌樂園,快樂不踩坑
+作為中國主題樂園的標杆之一,廣州長隆歡樂世界不是簡單的「過山車集合地」,而是一座融合尖端科技、沉浸敘事與嶺南風情的全天候遊樂綜合體。它佔地2000畝,擁有12大主題區、70餘項機動遊戲及數十場演藝秀,日均客流常破3萬——若無規劃,極易陷入排隊兩小時、遊玩五分鐘的疲憊循環。這份實用攻略,專為追求高效率、低消耗、強體驗的遊客訂製,助你把時間花在心跳上,而非隊尾。
+一. 行前必做三件事:省下3小時,多玩2個項目
+✅ 購票預約:微信公眾號「長隆旅遊」官方購票(比現場便宜約20元),務必提前1天預約入園日期(節假日需搶票);學生/老人/兒童按規則帶證件核驗;
+✅ 下載APP+綁定門票:「長隆旅遊」APP實時查排隊時長、演出時間、地圖導航,開啟「快速通行」功能(部分熱門項目可購優速卡,單次30–50元,推薦「垂直過山車」「十環過山車」必買);
+✅ 裝備精簡清單:穿運動鞋(禁拖鞋、高跟鞋)、帶掛繩手機殼、小腰包(存手機+充電寶+濕巾)、防曬帽+冰袖(園區遮陰少);雙肩包需寄存(入口處免費自助儲物櫃充足)。
+二. 交通住宿:離園越近,快樂越久
+📍地址:廣州市番禺區迎賓路88號(地鐵3號線「漢溪長隆站」D出口直達,出站即見園區拱門)。
+🚌最優抵達方式:
+· 地鐵(首選):市區乘3號線至「漢溪長隆站」,全程免換乘,出閘即入園,避免堵車與停車焦慮;
+· 自駕:導航「長隆歡樂世界停車場」,P1/P2最便利(30元/天),但旺季10點後常滿位,建議早於9:00抵達。
+🏨住宿推薦:
+長隆酒店/熊貓酒店(步行5分鐘):住客享提前30分鐘入園+專屬通道,夜間有煙花導覽,性價比最高;
+周邊經濟型酒店(如7天、如家):價格低,但通勤需打車(約15元),適合預算有限者。
+三. 動線規劃:黃金6小時,玩轉核心精華
+⏰ 推薦入園時間:8:30前到達(9:00開園),直奔北區——此時人最少,項目幾乎不用排隊。
+🔹上午(9:00–12:00):衝刺王牌刺激項
+9:00–9:30:直衝「垂直過山車」(亞洲首台彈射式,0–90km/h僅2秒),用優速卡免排40分鐘;
+9. 30–10:15:「十環過山車」(全球唯一雙環過山車,倒掛360°),緊接「U型滑板」(失重感最強);
+10. 15–11:00:「超級大擺錘」+「飛虎跳」(高空蕩秋千),感受腎上腺素持續飆升。
+🔹中午(12:00–13:30):錯峰休整+特色午餐
+· 避開12:30用餐高峰,12:00先吃「南國茶餐廳」廣式燒味飯(叉燒嫩、例湯鮮);
+· 飯後逛「奇妙島」拍照打卡,看卡通巡遊(12:45開始,路線覆蓋主幹道)。
+🔹下午(13:30–17:30):沉浸體驗+親子友好
+· 13:30–14:30:「星際決戰」(4D動感影院,劇情緊湊不暈眩);
+14. 30–15:30:「歡樂水花」(全齡段戲水區,夏季必玩,備好毛巾);
+15. 30–16:30:「動物王國」互動區:餵長頸鹿、摸羊駝、看鸚鵡表演(16:00場次最佳);
+16. 30–17:30:預留給「四維影院」或「魔幻劇場」(每日僅2–3場,APP查準時間)。
+四. 不可錯過的三大隱藏彩蛋
+🔸 夜場加成:18:00後入園票價半價(限當日),燈光秀+煙花秀(20:00開始)浪漫值拉滿,人流量驟減,摩天輪視野絕佳;
+🔸 美食冷知識:「歡樂餐廳」的榴槤披薩、熊貓酒店的竹筒飯、南國茶餐廳的楊枝甘露冰粉,是本地人私藏榜單;
+🔸 帶娃貼士:嬰兒車可租(50元/天),所有洗手間配母嬰室;「兒童天地」區設施軟包安全,家長可在「奇幻漂流」旁休息亭同步觀景。
+五. 重要提醒:快樂可持續的關鍵
+-園內消費偏高(瓶裝水15元、冰淇淋35元),可自帶未開封水和小食(安檢允許);
+演出時間每日微調,務必以APP當日推送為準;
+雨天部分戶外項目暫停,但室內場館照常開放,備好輕便雨衣更從容。
+長隆歡樂世界的終極心法,從來不是「刷完所有項目」,
+而是:
+在垂直過山車俯衝時放聲大笑,
+在摩天輪升至最高點時靜靜看雲,
+在孩子牽你手跑向旋轉木馬時,
+忽然想起——
+原來快樂,一直都很簡單,
+只是我們太久沒讓它,
 自由落地。</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>广东长隆欢乐世界旅游攻略：高效玩转华南王牌乐园，快乐不踩坑
-作为中国主题乐园的标杆之一，广州长隆欢乐世界不是简单的「过山车集合地」，而是一座融合尖端科技、沉浸叙事与岭南风情的全天候游乐综合体。它占地2000亩，拥有12大主题区、70余项机动游戏及数十场演艺秀，日均客流常破3万——若无规划，极易陷入排队两小时、游玩五分钟的疲惫循环。这份实用攻略，专为追求高效率、低消耗、强体验的游客订制，助你把时间花在心跳上，而非队尾。
-一、行前必做三件事：省下3小时，多玩2个项目
-购票预约：微信公众号「长隆旅游」官方购票（比现场便宜约20元），务必提前1天预约入园日期（节假日需抢票）；学生/老人/儿童按规则带证件核验
-下载APP+绑定门票：「长隆旅游」APP实时查排队时长、演出时间、地图导航，开启「快速通行」功能（部分热门项目可购优速卡，单次30–50元，推荐「垂直过山车」「十环过山车」必买）
-装备精简清单：穿运动鞋（禁拖鞋、高跟鞋）、带挂绳手机壳、小腰包（存手机+充电宝+湿巾）、防晒帽+冰袖（园区遮阴少）；双肩包需寄存（入口处免费自助储物柜充足）。
-二、交通住宿：离园越近，快乐越久
-地址：广州市番禺区迎宾路88号（地铁3号线「汉溪长隆站」D出口直达，出站即见园区拱门）。
-最优抵达方式
-· 地铁（首选）:市区乘3号线至「汉溪长隆站」，全程免换乘，出闸即入园，避免堵车与停车焦虑
-· 自驾：导航「长隆欢乐世界停车场」，P1/P2最便利（30元/天），但旺季10点后常满位，建议早于9:00抵达。
-住宿推荐
-长隆酒店/熊猫酒店（步行5分钟）:住客享提前30分钟入园+专属通道，夜间有烟花导览，性价比最高
-周边经济型酒店（如7天、如家）:价格低，但通勤需打车（约15元），适合预算有限者。
-三、动线规划：黄金6小时，玩转核心精华
-推荐入园时间：8:30前到达（9:00开园），直奔北区——此时人最少，项目几乎不用排队。
-上午(9:00–12:00):冲刺王牌刺激项
-9:00–9:30:直冲「垂直过山车」（亚洲首台弹射式，0–90km/h仅2秒），用优速卡免排40分钟
-9:30–10:15:「十环过山车」（全球唯一双环过山车，倒挂360°），紧接「U型滑板」（失重感最强）
-10:15–11:00:「超级大摆锤」+「飞虎跳」（高空荡秋千），感受肾上腺素持续飙升。
-中午(12:00–13:30):错峰休整+特色午餐
-· 避开12:30用餐高峰，12:00先吃「南国茶餐厅」广式烧味饭（叉烧嫩、例汤鲜）
-· 饭后逛「奇妙岛」拍照打卡，看卡通巡游（12:45开始，路线覆盖主干道）。
-下午(13:30–17:30):沉浸体验+亲子友好
-· 13:30–14:30:「星际决战」（4D动感影院，剧情紧凑不晕眩）
-14:30–15:30:「欢乐水花」（全龄段戏水区，夏季必玩，备好毛巾）
-15:30–16:30:「动物王国」互动区：喂长颈鹿、摸羊驼、看鹦鹉表演（16:00场次最佳）
-16:30–17:30:预留给「四维影院」或「魔幻剧场」（每日仅2–3场，APP查准时间）。
-四、不可错过的三大隐藏彩蛋
-夜场加成：18:00后入园票价半价（限当日），灯光秀+烟花秀（20:00开始）浪漫值拉满，人流量骤减，摩天轮视野绝佳
-美食冷知识：「欢乐餐厅」的榴梿披萨、熊猫酒店的竹筒饭、南国茶餐厅的杨枝甘露冰粉，是本地人私藏榜单
-带娃贴士：婴儿车可租（50元/天），所有洗手间配母婴室；「儿童天地」区设施软包安全，家长可在「奇幻漂流」旁休息亭同步观景。
-五、重要提醒：快乐可持续的关键
--园内消费偏高（瓶装水15元、冰淇淋35元），可自带未开封水和小食（安检允许）
-演出时间每日微调，务必以APP当日推送为准
-雨天部分户外项目暂停，但室内场馆照常开放，备好轻便雨衣更从容。
-长隆欢乐世界的终极心法，从来不是「刷完所有项目」
-而是
-在垂直过山车俯冲时放声大笑
-在摩天轮升至最高点时静静看云
-在孩子牵你手跑向旋转木马时
-忽然想起——
-原来快乐，一直都很简单
-只是我们太久没让它
+          <t>广东长隆欢乐世界旅游攻略：高效玩转华南王牌乐园，快乐不踩坑
+作为中国主题乐园的标杆之一，广州长隆欢乐世界不是简单的「过山车集合地」，而是一座融合尖端科技、沉浸叙事与岭南风情的全天候游乐综合体。它占地2000亩，拥有12大主题区、70余项机动游戏及数十场演艺秀，日均客流常破3万——若无规划，极易陷入排队两小时、游玩五分钟的疲惫循环。这份实用攻略，专为追求高效率、低消耗、强体验的游客订制，助你把时间花在心跳上，而非队尾。
+一、行前必做三件事：省下3小时，多玩2个项目
+购票预约：微信公众号「长隆旅游」官方购票（比现场便宜约20元），务必提前1天预约入园日期（节假日需抢票）；学生/老人/儿童按规则带证件核验
+下载APP+绑定门票：「长隆旅游」APP实时查排队时长、演出时间、地图导航，开启「快速通行」功能（部分热门项目可购优速卡，单次30–50元，推荐「垂直过山车」「十环过山车」必买）
+装备精简清单：穿运动鞋（禁拖鞋、高跟鞋）、带挂绳手机壳、小腰包（存手机+充电宝+湿巾）、防晒帽+冰袖（园区遮阴少）；双肩包需寄存（入口处免费自助储物柜充足）。
+二、交通住宿：离园越近，快乐越久
+地址：广州市番禺区迎宾路88号（地铁3号线「汉溪长隆站」D出口直达，出站即见园区拱门）。
+最优抵达方式
+· 地铁（首选）:市区乘3号线至「汉溪长隆站」，全程免换乘，出闸即入园，避免堵车与停车焦虑
+· 自驾：导航「长隆欢乐世界停车场」，P1/P2最便利（30元/天），但旺季10点后常满位，建议早于9:00抵达。
+住宿推荐
+长隆酒店/熊猫酒店（步行5分钟）:住客享提前30分钟入园+专属通道，夜间有烟花导览，性价比最高
+周边经济型酒店（如7天、如家）:价格低，但通勤需打车（约15元），适合预算有限者。
+三、动线规划：黄金6小时，玩转核心精华
+推荐入园时间：8:30前到达（9:00开园），直奔北区——此时人最少，项目几乎不用排队。
+上午(9:00–12:00):冲刺王牌刺激项
+9:00–9:30:直冲「垂直过山车」（亚洲首台弹射式，0–90km/h仅2秒），用优速卡免排40分钟
+9:30–10:15:「十环过山车」（全球唯一双环过山车，倒挂360°），紧接「U型滑板」（失重感最强）
+10:15–11:00:「超级大摆锤」+「飞虎跳」（高空荡秋千），感受肾上腺素持续飙升。
+中午(12:00–13:30):错峰休整+特色午餐
+· 避开12:30用餐高峰，12:00先吃「南国茶餐厅」广式烧味饭（叉烧嫩、例汤鲜）
+· 饭后逛「奇妙岛」拍照打卡，看卡通巡游（12:45开始，路线覆盖主干道）。
+下午(13:30–17:30):沉浸体验+亲子友好
+· 13:30–14:30:「星际决战」（4D动感影院，剧情紧凑不晕眩）
+14:30–15:30:「欢乐水花」（全龄段戏水区，夏季必玩，备好毛巾）
+15:30–16:30:「动物王国」互动区：喂长颈鹿、摸羊驼、看鹦鹉表演（16:00场次最佳）
+16:30–17:30:预留给「四维影院」或「魔幻剧场」（每日仅2–3场，APP查准时间）。
+四、不可错过的三大隐藏彩蛋
+夜场加成：18:00后入园票价半价（限当日），灯光秀+烟花秀（20:00开始）浪漫值拉满，人流量骤减，摩天轮视野绝佳
+美食冷知识：「欢乐餐厅」的榴梿披萨、熊猫酒店的竹筒饭、南国茶餐厅的杨枝甘露冰粉，是本地人私藏榜单
+带娃贴士：婴儿车可租（50元/天），所有洗手间配母婴室；「儿童天地」区设施软包安全，家长可在「奇幻漂流」旁休息亭同步观景。
+五、重要提醒：快乐可持续的关键
+-园内消费偏高（瓶装水15元、冰淇淋35元），可自带未开封水和小食（安检允许）
+演出时间每日微调，务必以APP当日推送为准
+雨天部分户外项目暂停，但室内场馆照常开放，备好轻便雨衣更从容。
+长隆欢乐世界的终极心法，从来不是「刷完所有项目」
+而是
+在垂直过山车俯冲时放声大笑
+在摩天轮升至最高点时静静看云
+在孩子牵你手跑向旋转木马时
+忽然想起——
+原来快乐，一直都很简单
+只是我们太久没让它
 自由落地。</t>
         </is>
       </c>
@@ -2163,7 +1923,7 @@
         <v>1633</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0.19</v>
+        <v>0.159</v>
       </c>
       <c r="P8" s="5" t="n">
         <v>10</v>
@@ -2241,51 +2001,51 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>廣州長隆度假區遊玩攻略 夏日必打卡！廣州長隆水上樂園，承包一整個夏天的快樂！過山車、造浪
-
-andysunset分享的 廣州長隆度假區 Trip Moment
-30 天前發布，幫助了 4844 位旅客的旅程
-156 位旅客與此 Trip Moment 互動，提供更多真實反饋
-還有另外 364 篇關於 廣州長隆度假區 的 Trip Moment，可為您的旅程提供更多參考
-2026.10.28 廣州長隆度假區即時旅遊資訊
-今日天氣：21~30℃
-今日營業狀態：營業中 | 24 小時全年無休
-點評分：4.7/5 | 14831 評論 | TWD488起 | 3733位旅客感興趣
-廣州長隆度假區遊玩攻略 🎢🐨🐼
-🔥夏日必打卡!廣州長隆水上樂園,承包一整個夏天的快樂!過山車、造浪池、大喇叭...尖叫聲與歡笑聲交織,刺激與歡樂共存! 🏖️
-📍地址:廣東省廣州市番禺區漢溪大道東299號
-💰門票:100.0(含歡樂世界、水上樂園、野生動物世界)
-🎢遊樂設施推薦:
-✨搖滾巨輪(超級大喇叭):尖叫聲響徹天際!像被吸進漩渦,失重感超刺激!🎢🌊
-✨巨獸碗(激流勇進):像被捲入巨大的碗中,被水浪推著前進,超爽快!🛁🏄‍♂️
-✨巨洪峽(造浪池):超長的造浪池,人浪翻滾!站在浪尖上感受被衝擊的快感,超帶感!🌊🌊🌊
-✨大滑板(水上過山車):像在衝浪板上玩過山車,超刺激!全程尖叫不斷!🏄‍♀️🏄‍♂️
-📸拍照打卡點推薦:
-🔥大熱天必備——造浪池!站在浪尖上拍照,拍出超酷炫的照片!📸📸📸
-🌟水上過山車——別忘記用手機記錄下這瞬間的刺激!📱📱📱
-🎢娛樂設施——玩累了就拍張照休息下,記錄這難忘的時刻!📷📷📷
-🍱美食推薦:
-✨亞洲餐廳——麻辣燙、甜品小吃、飲品...應有盡有,滿足你的味蕾需求!🍲🍦☕️
+          <t>廣州長隆度假區遊玩攻略 夏日必打卡！廣州長隆水上樂園，承包一整個夏天的快樂！過山車、造浪
+
+andysunset分享的 廣州長隆度假區 Trip Moment
+30 天前發布，幫助了 4844 位旅客的旅程
+156 位旅客與此 Trip Moment 互動，提供更多真實反饋
+還有另外 364 篇關於 廣州長隆度假區 的 Trip Moment，可為您的旅程提供更多參考
+2026.10.28 廣州長隆度假區即時旅遊資訊
+今日天氣：21~30℃
+今日營業狀態：營業中 | 24 小時全年無休
+點評分：4.7/5 | 14831 評論 | TWD488起 | 3733位旅客感興趣
+廣州長隆度假區遊玩攻略 🎢🐨🐼
+🔥夏日必打卡!廣州長隆水上樂園,承包一整個夏天的快樂!過山車、造浪池、大喇叭...尖叫聲與歡笑聲交織,刺激與歡樂共存! 🏖️
+📍地址:廣東省廣州市番禺區漢溪大道東299號
+💰門票:100.0(含歡樂世界、水上樂園、野生動物世界)
+🎢遊樂設施推薦:
+✨搖滾巨輪(超級大喇叭):尖叫聲響徹天際!像被吸進漩渦,失重感超刺激!🎢🌊
+✨巨獸碗(激流勇進):像被捲入巨大的碗中,被水浪推著前進,超爽快!🛁🏄‍♂️
+✨巨洪峽(造浪池):超長的造浪池,人浪翻滾!站在浪尖上感受被衝擊的快感,超帶感!🌊🌊🌊
+✨大滑板(水上過山車):像在衝浪板上玩過山車,超刺激!全程尖叫不斷!🏄‍♀️🏄‍♂️
+📸拍照打卡點推薦:
+🔥大熱天必備——造浪池!站在浪尖上拍照,拍出超酷炫的照片!📸📸📸
+🌟水上過山車——別忘記用手機記錄下這瞬間的刺激!📱📱📱
+🎢娛樂設施——玩累了就拍張照休息下,記錄這難忘的時刻!📷📷📷
+🍱美食推薦:
+✨亞洲餐廳——麻辣燙、甜品小吃、飲品...應有盡有,滿足你的味蕾需求!🍲🍦☕️
 ✨燒烤區域——烤串、烤魚、海鮮...盡情享受美食盛宴!🍢🦐</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>广州长隆度假区游玩攻略
-夏日必打卡！广州长隆水上乐园，承包一整个夏天的快乐！过山车、造浪池、大喇叭……尖叫声与欢笑声交织，刺激与欢乐共存！
-地址：广东省广州市番禺区汉溪大道东299号
-门票：100.0（含欢乐世界、水上乐园、野生动物世界）
-游乐设施推荐
-摇滚巨轮（超级大喇叭）:尖叫声响彻天际！像被吸进漩涡，失重感超刺激！
-巨兽碗（激流勇进）:像被卷入巨大的碗中，被水浪推著前进，超爽快！
-巨洪峡（造浪池）:超长的造浪池，人浪翻滚！站在浪尖上感受被冲击的快感，超带感！
-大滑板（水上过山车）:像在冲浪板上玩过山车，超刺激！全程尖叫不断！
-拍照打卡点推荐
-大热天必备——造浪池！站在浪尖上拍照，拍出超酷炫的照片！
-水上过山车——别忘记用手机记录下这瞬间的刺激！
-娱乐设施——玩累了就拍张照休息下，记录这难忘的时刻！
-美食推荐
-亚洲餐厅——麻辣烫、甜品小吃、饮品……应有尽有，满足你的味蕾需求！
+          <t>广州长隆度假区游玩攻略
+夏日必打卡！广州长隆水上乐园，承包一整个夏天的快乐！过山车、造浪池、大喇叭……尖叫声与欢笑声交织，刺激与欢乐共存！
+地址：广东省广州市番禺区汉溪大道东299号
+门票：100.0（含欢乐世界、水上乐园、野生动物世界）
+游乐设施推荐
+摇滚巨轮（超级大喇叭）:尖叫声响彻天际！像被吸进漩涡，失重感超刺激！
+巨兽碗（激流勇进）:像被卷入巨大的碗中，被水浪推著前进，超爽快！
+巨洪峡（造浪池）:超长的造浪池，人浪翻滚！站在浪尖上感受被冲击的快感，超带感！
+大滑板（水上过山车）:像在冲浪板上玩过山车，超刺激！全程尖叫不断！
+拍照打卡点推荐
+大热天必备——造浪池！站在浪尖上拍照，拍出超酷炫的照片！
+水上过山车——别忘记用手机记录下这瞬间的刺激！
+娱乐设施——玩累了就拍张照休息下，记录这难忘的时刻！
+美食推荐
+亚洲餐厅——麻辣烫、甜品小吃、饮品……应有尽有，满足你的味蕾需求！
 烧烤区域——烤串、烤鱼、海鲜……尽情享受美食盛宴！</t>
         </is>
       </c>
@@ -2296,7 +2056,7 @@
         <v>406</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.466</v>
+        <v>0.435</v>
       </c>
       <c r="P9" s="5" t="n">
         <v>10</v>
@@ -7327,7 +7087,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>48356</v>
+        <v>32218</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
@@ -7358,7 +7118,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>38.24%</t>
+          <t>7.30%</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr"/>
@@ -7370,7 +7130,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>320</v>
+        <v>83</v>
       </c>
       <c r="C15" s="6" t="inlineStr"/>
     </row>
@@ -7580,36 +7340,41 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-&lt;p style="text-align:justify;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;嗨！各位快乐玩家，欢迎来到广州长隆度假区，快收下这份吃住玩一站式度假攻略，一键开启快乐假日吧！&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/span&gt;&lt;/p&gt;
-&lt;p style="text-align:justify;"&gt; &lt;/p&gt;
-&lt;p style="text-align:center;"&gt;&lt;span style="font-size:10.5pt;"&gt;&lt;span style="font-family:'等线';"&gt;&lt;b&gt;&lt;span style="font-size:12pt;"&gt;&lt;span style="font-family:'微软雅黑', sans-serif;"&gt;第一站：长隆欢乐世界&lt;/span&gt;&lt;/span&gt;&lt;/b&gt;&lt;/span&gt;</t>
+          <t>嗨！各位快乐玩家，欢迎来到广州长隆度假区，快收下这份吃住玩一站式度假攻略，一键开启快乐假日吧！
+第一站：长隆欢乐世界
+假期想狂欢？那就来广州长隆欢乐世界！忘掉工作的繁忙和生活的琐碎，来一场全身心的狂欢刺激之旅吧。这里有全球领先的70+游乐设施，有趣，好看又刺激，让你心跳加速尽情释放！
+坐上“全球过山车之王“的垂直过山车。三分钟之内让你完成上天入地冲浪的刺激体验
+坐上游乐园最大的秋千，挑战地心引力 在超级大摆锤的极致摇摆中，感受无尽的刺激和乐趣
+谁说欢乐世界只适合大朋友，这里有小朋友也能玩的飞马家庭过山车，刺激又奇幻，家庭出游千万不要错过。最浪漫的打卡点还是梦幻转马，无论是小朋友还是拥有少女心的你，都可以进入梦幻童话世界， 打卡到人生照片
+第二站：长隆野生动物世界
+来都来了，怎么能错过长隆野生动物世界~珍稀的动物大家族，独特的观赏方式和精彩的科普课堂，各种超好玩的项目等你来打卡
+搭乘缆车飞跃东非大草原，俯瞰壮观的动物大迁徙。在长颈鹿广场，可以给长颈鹿投喂树叶，与它互</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>嗨！各位快乐玩家，欢迎来到广州长隆度假区，快收下这份吃住玩一站式度假攻略，一键开启快乐假日吧！
-第一站：长隆欢乐世界
-假期想狂欢？那就来广州长隆欢乐世界！忘掉工作的繁忙和生活的琐碎，来一场全身心的狂欢刺激之旅吧。这里有全球领先的70+游乐设施，有趣，好看又刺激，让你心跳加速尽情释放！
-坐上“全球过山车之王“的垂直过山车。三分钟之内让你完成上天入地冲浪的刺激体验
-坐上游乐园最大的秋千，挑战地心引力 在超级大摆锤的极致摇摆中，感受无尽的刺激和乐趣
-谁说欢乐世界只适合大朋友，这里有小朋友也能玩的飞马家庭过山车，刺激又奇幻，家庭出游千万不要错过。最浪漫的打卡点还是梦幻转马，无论是小朋友还是拥有少女心的你，都可以进入梦幻童话世界，打卡到人生照片
-第二站：长隆野生动物世界
-来都来了，怎么能错过长隆野生动物世界~珍稀的动物大家族，独特的观赏方式和精彩的科普课堂，各种超好玩的项目等你来打卡
-搭乘缆车飞跃东非大草原，俯瞰壮观的动物大迁徙。在长颈鹿广场，可以给长颈鹿投喂树叶，与它互动拍照打卡
-乘坐森林小火车，穿越五大洲的珍稀动物世界，近距离接触可爱的动物朋友
-喜欢大熊猫的小朋友千万别错</t>
+          <t>嗨！各位快乐玩家，欢迎来到广州长隆度假区，快收下这份吃住玩一站式度假攻略，一键开启快乐假日吧！
+第一站：长隆欢乐世界
+假期想狂欢？那就来广州长隆欢乐世界！忘掉工作的繁忙和生活的琐碎，来一场全身心的狂欢刺激之旅吧。这里有全球领先的70+游乐设施，有趣，好看又刺激，让你心跳加速尽情释放！
+坐上“全球过山车之王“的垂直过山车。三分钟之内让你完成上天入地冲浪的刺激体验
+坐上游乐园最大的秋千，挑战地心引力 在超级大摆锤的极致摇摆中，感受无尽的刺激和乐趣
+谁说欢乐世界只适合大朋友，这里有小朋友也能玩的飞马家庭过山车，刺激又奇幻，家庭出游千万不要错过。最浪漫的打卡点还是梦幻转马，无论是小朋友还是拥有少女心的你，都可以进入梦幻童话世界，打卡到人生照片
+第二站：长隆野生动物世界
+来都来了，怎么能错过长隆野生动物世界~珍稀的动物大家族，独特的观赏方式和精彩的科普课堂，各种超好玩的项目等你来打卡
+搭乘缆车飞跃东非大草原，俯瞰壮观的动物大迁徙。在长颈鹿广场，可以给长颈鹿投喂树叶，与它互动拍照打卡
+乘坐森林小火车，穿越五大洲的珍稀动物世界，近距离接触可爱的动物朋友
+喜欢大熊猫的小朋友千万别错过，拥有全球唯一大熊</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>10542</v>
+        <v>1479</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>1478</v>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>86.20%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
@@ -7631,58 +7396,61 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>五一長隆歡樂世界保姆級攻略｜避開人潮玩回票價！
-
-cortexezu6yn4xgma0分享的 長隆歡樂世界 Trip Moment
-30 天前發布，幫助了 108 位旅客的旅程
-還有另外 357 篇關於 長隆歡樂世界 的 Trip Moment，可為您的旅程提供更多參考
-2026.10.28 長隆歡樂世界即時旅遊資訊
-今日天氣：21~30℃
-今日營業狀態：營業中 | 10:00–22:00 營業 (於 20:00 停售門票)
-點評分：4.7/5 | 28068 評論 | TWD1156起 | 3178位旅客感興趣
-姊妹們快看!五一去長隆歡樂世界必看這份超詳細攻略💯親測有效,一天刷遍所有王牌項目真的太爽啦!🔥
-📅 行程安排(黃金6小時衝關版)
-⏰8:30前
-一定要在北門排隊‼️
-9點開園直接衝鴨!🏃‍♀️
-🎢9:00-12:00 刺激項目黃金時段
-✔️首衝"超級激流"(全球首個旋轉式雙提升系統!全新體驗!)
-✔️接著玩"彈射過山車"(推背感炸裂💥)
-✔️"超級海盜船"(搖擺幅度超大!)
-✔️"U型滑板"(360度旋轉絕了)
-✔️最後體驗</t>
+          <t>五一長隆歡樂世界保姆級攻略｜避開人潮玩回票價！
+
+cortexezu6yn4xgma0分享的 長隆歡樂世界 Trip Moment
+30 天前發布，幫助了 108 位旅客的旅程
+還有另外 357 篇關於 長隆歡樂世界 的 Trip Moment，可為您的旅程提供更多參考
+2026.10.28 長隆歡樂世界即時旅遊資訊
+今日天氣：21~30℃
+今日營業狀態：營業中 | 10:00–22:00 營業 (於 20:00 停售門票)
+點評分：4.7/5 | 28068 評論 | TWD1156起 | 3178位旅客感興趣
+姊妹們快看!五一去長隆歡樂世界必看這份超詳細攻略💯親測有效,一天刷遍所有王牌項目真的太爽啦!🔥
+📅 行程安排(黃金6小時衝關版)
+⏰8:30前
+一定要在北門排隊‼️
+9點開園直接衝鴨!🏃‍♀️
+🎢9:00-12:00 刺激項目黃金時段
+✔️首衝"超級激流"(全球首個旋轉式雙提升系統!全新體驗!)
+✔️接著玩"彈射過山車"(推背感炸裂💥)
+✔️"超級海盜船"(搖擺幅度超大!)
+✔️"U型滑板"(360度旋轉絕了)
+✔️最後體驗"超級大擺錘"和"飛虎跳"
+(這幾個項目中午</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>姊妹们快看！五一去长隆欢乐世界必看这份超详细攻略亲测有效，一天刷遍所有王牌项目真的太爽啦！
-行程安排（黄金6小时冲关版）
-8:30前
-一定要在北门排队
-9点开园直接冲鸭！
-9:00-12:00 刺激项目黄金时段
-首冲“超级激流”（全球首个旋转式双提升系统！全新体验！）
-接著玩“弹射过山车”（推背感炸裂）
-“超级海盗船”（摇摆幅度超大！）
-“U型滑板”（360度旋转绝了）
-最后体验“超级大摆锤”和“飞虎跳”
-（这几个项目中午后排队都超久）
-12:00-13:30 错峰午餐+拍美照
-推荐南国茶餐厅吃正宗的广式烧味饭
-奇妙岛随便拍都出片
-12:45观看超级可爱的卡通巡游
-13:30-17:30 沉浸体验+亲子时间
-星际决战（4D动感影院超震撼）
-欢乐水花戏水区（小朋友最爱）
-动物王国喂长颈鹿+看鹦鹉表演
-四维影院或魔幻剧场（玩累了正好休息）
-五一专属彩蛋
-今年“春日畅玩季”主题活动美哭
-“悦己→热恋→童梦”三阶情感体验
-场景布置梦幻到炸，拍照绝绝子
-全新“超级激流”设备已经开放
-融合卡卡虎IP故事，沉浸感MAX
-（十环和垂直过山车在升级中</t>
+          <t>姊妹们快看！五一去长隆欢乐世界必看这份超详细攻略亲测有效，一天刷遍所有王牌项目真的太爽啦！
+行程安排（黄金6小时冲关版）
+8:30前
+一定要在北门排队
+9点开园直接冲鸭！
+9:00-12:00 刺激项目黄金时段
+首冲“超级激流”（全球首个旋转式双提升系统！全新体验！）
+接著玩“弹射过山车”（推背感炸裂）
+“超级海盗船”（摇摆幅度超大！）
+“U型滑板”（360度旋转绝了）
+最后体验“超级大摆锤”和“飞虎跳”
+（这几个项目中午后排队都超久）
+12:00-13:30 错峰午餐+拍美照
+推荐南国茶餐厅吃正宗的广式烧味饭
+奇妙岛随便拍都出片
+12:45观看超级可爱的卡通巡游
+13:30-17:30 沉浸体验+亲子时间
+星际决战（4D动感影院超震撼）
+欢乐水花戏水区（小朋友最爱）
+动物王国喂长颈鹿+看鹦鹉表演
+四维影院或魔幻剧场（玩累了正好休息）
+五一专属彩蛋
+今年“春日畅玩季”主题活动美哭
+“悦己→热恋→童梦”三阶情感体验
+场景布置梦幻到炸，拍照绝绝子
+全新“超级激流”设备已经开放
+融合卡卡虎IP故事，沉浸感MAX
+（十环和垂直过山车在升级中，期待王者归来）
+出行小贴士
+手机购票：提前在“长隆旅</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -7693,7 +7461,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>33.50%</t>
+          <t>31.60%</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
